--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3092,16 +3092,16 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3224,16 +3224,16 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="M23" t="n">
         <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3488,13 +3488,13 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AC23" t="n">
         <v>1.57</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="M24" t="n">
         <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3620,13 +3620,13 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC24" t="n">
         <v>1.57</v>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="M23" t="n">
         <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3488,13 +3488,13 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC23" t="n">
         <v>1.57</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
         <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3620,13 +3620,13 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AC24" t="n">
         <v>1.57</v>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3092,16 +3092,16 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3224,16 +3224,16 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="M23" t="n">
         <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3488,13 +3488,13 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AC23" t="n">
         <v>1.57</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="M24" t="n">
         <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3620,13 +3620,13 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC24" t="n">
         <v>1.57</v>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.38</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>3.12</v>
+        <v>4.3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.57</v>
+        <v>5.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.12</v>
       </c>
       <c r="N11" t="n">
-        <v>5.6</v>
+        <v>2.57</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="M23" t="n">
         <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3488,13 +3488,13 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC23" t="n">
         <v>1.57</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
         <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3620,13 +3620,13 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AC24" t="n">
         <v>1.57</v>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M8" t="n">
-        <v>4.32</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>7.65</v>
+        <v>8.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.12</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3092,16 +3092,16 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3224,16 +3224,16 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="M22" t="n">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="N22" t="n">
-        <v>3.15</v>
+        <v>3.64</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.18</v>
+        <v>1.65</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL24"/>
+  <dimension ref="A1:AL25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U8" t="n">
         <v>1.36</v>
       </c>
-      <c r="M8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N8" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1557,27 +1557,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45881.58333333334</v>
+        <v>45881.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC10" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>45881.60416666666</v>
+        <v>45881.58333333334</v>
       </c>
     </row>
     <row r="16">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45881.63541666666</v>
+        <v>45881.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="AL18" s="3" t="n">
-        <v>45881.66666666666</v>
+        <v>45881.63541666666</v>
       </c>
     </row>
     <row r="19">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3009,27 +3009,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3092,16 +3092,16 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="AL20" s="3" t="n">
-        <v>45881.79166666666</v>
+        <v>45881.66666666666</v>
       </c>
     </row>
     <row r="21">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="M22" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3356,16 +3356,16 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="AL22" s="3" t="n">
-        <v>45881.8125</v>
+        <v>45881.79166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3488,16 +3488,16 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>45881.89583333334</v>
+        <v>45881.8125</v>
       </c>
     </row>
     <row r="24">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="M24" t="n">
         <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3620,13 +3620,13 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC24" t="n">
         <v>1.57</v>
@@ -3660,6 +3660,138 @@
         </is>
       </c>
       <c r="AL24" s="3" t="n">
+        <v>45881.89583333334</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL25" s="3" t="n">
         <v>45881.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL25"/>
+  <dimension ref="A1:AL38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
         <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45881.58333333334</v>
+        <v>45881.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45881.60416666666</v>
+        <v>45881.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="AL17" s="3" t="n">
-        <v>45881.63541666666</v>
+        <v>45881.58333333334</v>
       </c>
     </row>
     <row r="18">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="AL18" s="3" t="n">
-        <v>45881.63541666666</v>
+        <v>45881.58333333334</v>
       </c>
     </row>
     <row r="19">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="AL19" s="3" t="n">
-        <v>45881.66666666666</v>
+        <v>45881.58333333334</v>
       </c>
     </row>
     <row r="20">
@@ -3009,27 +3009,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="AL20" s="3" t="n">
-        <v>45881.66666666666</v>
+        <v>45881.58333333334</v>
       </c>
     </row>
     <row r="21">
@@ -3141,27 +3141,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="AL21" s="3" t="n">
-        <v>45881.79166666666</v>
+        <v>45881.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -3273,27 +3273,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3356,16 +3356,16 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="AL22" s="3" t="n">
-        <v>45881.79166666666</v>
+        <v>45881.60416666666</v>
       </c>
     </row>
     <row r="23">
@@ -3405,27 +3405,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>45881.8125</v>
+        <v>45881.60416666666</v>
       </c>
     </row>
     <row r="24">
@@ -3537,27 +3537,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3620,16 +3620,16 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="AL24" s="3" t="n">
-        <v>45881.89583333334</v>
+        <v>45881.60416666666</v>
       </c>
     </row>
     <row r="25">
@@ -3669,129 +3669,1845 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Mamelodi Sundowns</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>AmaZulu</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL25" s="3" t="n">
+        <v>45881.60416666666</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ferencváros</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ludogorets</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL26" s="3" t="n">
+        <v>45881.63541666666</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kairat</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL27" s="3" t="n">
+        <v>45881.63541666666</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ferencváros</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ludogorets</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL28" s="3" t="n">
+        <v>45881.63541666666</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kairat</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL29" s="3" t="n">
+        <v>45881.63541666666</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL30" s="3" t="n">
+        <v>45881.66666666666</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL31" s="3" t="n">
+        <v>45881.66666666666</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Red Star Belgrade</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lech Poznań</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL32" s="3" t="n">
+        <v>45881.66666666666</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Red Star Belgrade</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lech Poznań</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL33" s="3" t="n">
+        <v>45881.66666666666</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vélez Sarsfield</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL34" s="3" t="n">
+        <v>45881.79166666666</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL35" s="3" t="n">
+        <v>45881.79166666666</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL36" s="3" t="n">
+        <v>45881.8125</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>South America Copa Libertadores</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL37" s="3" t="n">
+        <v>45881.89583333334</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>Peñarol</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Racing Club</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="L38" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA38" t="n">
         <v>2.25</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="AB38" t="n">
         <v>2.4</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AC38" t="n">
         <v>1.57</v>
       </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL25" s="3" t="n">
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL38" s="3" t="n">
         <v>45881.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
-        <v>3.23</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>3.94</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>1.48</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="M20" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M33" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4940,16 +4940,16 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5072,16 +5072,16 @@
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.03</v>
+        <v>2.56</v>
       </c>
       <c r="M37" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="N37" t="n">
-        <v>3.52</v>
+        <v>2.67</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5336,13 +5336,13 @@
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AC37" t="n">
         <v>1.57</v>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.56</v>
+        <v>2.03</v>
       </c>
       <c r="M38" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="N38" t="n">
-        <v>2.67</v>
+        <v>3.52</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5468,13 +5468,13 @@
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC38" t="n">
         <v>1.57</v>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL38"/>
+  <dimension ref="A1:AL39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>1.48</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="M26" t="n">
         <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M31" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -5508,6 +5508,138 @@
         </is>
       </c>
       <c r="AL38" s="3" t="n">
+        <v>45881.89583333334</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Wilstermann</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V39" t="n">
+        <v>7</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL39" s="3" t="n">
         <v>45881.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>3.65</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>1.98</v>
       </c>
       <c r="M16" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>1.48</v>
+        <v>3.7</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.65</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="M26" t="n">
         <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M32" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4940,16 +4940,16 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5072,16 +5072,16 @@
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>3.23</v>
       </c>
       <c r="N8" t="n">
-        <v>8.300000000000001</v>
+        <v>3.94</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.23</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>3.94</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>13.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.55</v>
+        <v>2.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.98</v>
+        <v>2.97</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="N16" t="n">
-        <v>3.7</v>
+        <v>2.34</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>2.13</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.15</v>
+        <v>1.71</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>1.48</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>16.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="M26" t="n">
         <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="M27" t="n">
         <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>14.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N32" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4907,37 +4907,37 @@
         <v>3.65</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Z34" t="n">
         <v>1.55</v>
@@ -4952,22 +4952,22 @@
         <v>1.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5084,10 +5084,10 @@
         <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="M38" t="n">
-        <v>2.91</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>3.52</v>
+        <v>2.7</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="M39" t="n">
-        <v>3.75</v>
+        <v>2.91</v>
       </c>
       <c r="N39" t="n">
-        <v>2.7</v>
+        <v>3.52</v>
       </c>
       <c r="O39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="N9" t="n">
-        <v>8.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>13.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>13.75</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>6.1</v>
+        <v>3.65</v>
       </c>
       <c r="O11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.88</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>1.98</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>1.48</v>
+        <v>3.7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>4.8</v>
+        <v>1.48</v>
       </c>
       <c r="O15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.97</v>
+        <v>1.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.44</v>
+        <v>4.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2.34</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="P16" t="n">
-        <v>8.1</v>
+        <v>12</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.92</v>
+        <v>2.65</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>2.67</v>
+        <v>3.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.93</v>
+        <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V16" t="n">
-        <v>7.1</v>
+        <v>5.25</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.1</v>
+        <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.9</v>
+        <v>4.45</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.13</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.72</v>
+        <v>2.41</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.48</v>
+        <v>2.97</v>
       </c>
       <c r="M17" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>2.34</v>
       </c>
       <c r="O17" t="n">
-        <v>1.5</v>
+        <v>2.23</v>
       </c>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>8.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.63</v>
+        <v>1.92</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="U17" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>8.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>2.13</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>1.71</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.45</v>
+        <v>3.72</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.33</v>
+        <v>7.1</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>1.48</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG18" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="N19" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.98</v>
+        <v>1.61</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>3.7</v>
+        <v>6.1</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>16.75</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>16.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="M26" t="n">
         <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
         <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="M28" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="N28" t="n">
-        <v>5.4</v>
+        <v>4.55</v>
       </c>
       <c r="O28" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="P28" t="n">
-        <v>8.6</v>
+        <v>14.75</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="T28" t="n">
-        <v>2.93</v>
+        <v>2.42</v>
       </c>
       <c r="U28" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="V28" t="n">
-        <v>7.8</v>
+        <v>5.45</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.02</v>
+        <v>3.85</v>
       </c>
       <c r="AB28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2.09</v>
       </c>
-      <c r="AC28" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AD28" t="n">
-        <v>3.62</v>
+        <v>2.7</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.73</v>
+        <v>2.03</v>
       </c>
       <c r="AH28" t="n">
-        <v>7.3</v>
+        <v>4.8</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>3.64</v>
       </c>
       <c r="N29" t="n">
-        <v>4.55</v>
+        <v>5.4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P29" t="n">
-        <v>14.75</v>
+        <v>8.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T29" t="n">
-        <v>2.42</v>
+        <v>2.93</v>
       </c>
       <c r="U29" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>5.45</v>
+        <v>7.8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.85</v>
+        <v>3.02</v>
       </c>
       <c r="AB29" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC29" t="n">
         <v>1.74</v>
       </c>
-      <c r="AC29" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AD29" t="n">
-        <v>2.7</v>
+        <v>3.62</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.03</v>
+        <v>1.73</v>
       </c>
       <c r="AH29" t="n">
-        <v>4.8</v>
+        <v>7.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="N34" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="O34" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.56</v>
+        <v>2.03</v>
       </c>
       <c r="M37" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="N37" t="n">
-        <v>2.67</v>
+        <v>3.52</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5336,13 +5336,13 @@
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC37" t="n">
         <v>1.57</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA38" t="n">
         <v>2.25</v>
       </c>
-      <c r="M38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P38" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V38" t="n">
-        <v>7</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AB38" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="M39" t="n">
-        <v>2.91</v>
+        <v>3.75</v>
       </c>
       <c r="N39" t="n">
-        <v>3.52</v>
+        <v>2.7</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="M8" t="n">
-        <v>3.23</v>
+        <v>5.3</v>
       </c>
       <c r="N8" t="n">
+        <v>11</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P8" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA8" t="n">
         <v>3.94</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="P8" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V8" t="n">
-        <v>7</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.35</v>
+        <v>2.56</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>13.75</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
-        <v>4.6</v>
+        <v>3.23</v>
       </c>
       <c r="N10" t="n">
-        <v>8.300000000000001</v>
+        <v>3.94</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>6.1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>1.48</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.65</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>4.8</v>
+        <v>1.48</v>
       </c>
       <c r="O16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S16" t="n">
         <v>3.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="U16" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="V16" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="W16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.14</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.15</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.97</v>
+        <v>1.79</v>
       </c>
       <c r="M17" t="n">
-        <v>3.44</v>
+        <v>3.88</v>
       </c>
       <c r="N17" t="n">
-        <v>2.34</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>2.23</v>
+        <v>1.58</v>
       </c>
       <c r="P17" t="n">
-        <v>8.1</v>
+        <v>14.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.92</v>
+        <v>2.56</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>2.67</v>
+        <v>3.18</v>
       </c>
       <c r="T17" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="V17" t="n">
-        <v>7.1</v>
+        <v>5.35</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.13</v>
       </c>
-      <c r="AC17" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AD17" t="n">
-        <v>3.72</v>
+        <v>2.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AH17" t="n">
-        <v>7.1</v>
+        <v>4.65</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.48</v>
+        <v>2.97</v>
       </c>
       <c r="M18" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>2.34</v>
       </c>
       <c r="O18" t="n">
-        <v>1.5</v>
+        <v>2.23</v>
       </c>
       <c r="P18" t="n">
-        <v>12</v>
+        <v>8.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.63</v>
+        <v>1.92</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="T18" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="U18" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>8.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.55</v>
+        <v>2.13</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>1.71</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.45</v>
+        <v>3.72</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.33</v>
+        <v>7.1</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.88</v>
+        <v>4.15</v>
       </c>
       <c r="N19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH19" t="n">
         <v>4.2</v>
       </c>
-      <c r="O19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>4.65</v>
-      </c>
       <c r="AI19" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="N20" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.28</v>
+        <v>2.63</v>
       </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.08</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.03</v>
+        <v>1.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>6.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="M26" t="n">
         <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="M27" t="n">
         <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1</v>
+        <v>3.64</v>
       </c>
       <c r="N28" t="n">
-        <v>4.55</v>
+        <v>5.4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P28" t="n">
-        <v>14.75</v>
+        <v>8.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.42</v>
+        <v>2.93</v>
       </c>
       <c r="U28" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
-        <v>5.45</v>
+        <v>7.8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.85</v>
+        <v>3.02</v>
       </c>
       <c r="AB28" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC28" t="n">
         <v>1.74</v>
       </c>
-      <c r="AC28" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AD28" t="n">
-        <v>2.7</v>
+        <v>3.62</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.03</v>
+        <v>1.73</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.8</v>
+        <v>7.3</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="M29" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>5.4</v>
+        <v>4.55</v>
       </c>
       <c r="O29" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="P29" t="n">
-        <v>8.6</v>
+        <v>14.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="T29" t="n">
-        <v>2.93</v>
+        <v>2.42</v>
       </c>
       <c r="U29" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="V29" t="n">
-        <v>7.8</v>
+        <v>5.45</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.02</v>
+        <v>3.85</v>
       </c>
       <c r="AB29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC29" t="n">
         <v>2.09</v>
       </c>
-      <c r="AC29" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AD29" t="n">
-        <v>3.62</v>
+        <v>2.7</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.73</v>
+        <v>2.03</v>
       </c>
       <c r="AH29" t="n">
-        <v>7.3</v>
+        <v>4.8</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="N35" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="O35" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="M37" t="n">
-        <v>2.91</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>3.52</v>
+        <v>2.7</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,40 +5426,40 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.56</v>
+        <v>2.03</v>
       </c>
       <c r="M38" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="N38" t="n">
-        <v>2.67</v>
+        <v>3.52</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -5468,13 +5468,13 @@
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC38" t="n">
         <v>1.57</v>
@@ -5486,10 +5486,10 @@
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V39" t="n">
+        <v>11</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA39" t="n">
         <v>2.25</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P39" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V39" t="n">
-        <v>7</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AB39" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AH39" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -938,22 +938,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>7.26</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.29</v>
+        <v>1.89</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3</v>
+        <v>3.38</v>
       </c>
       <c r="N8" t="n">
-        <v>11</v>
+        <v>3.64</v>
       </c>
       <c r="O8" t="n">
-        <v>1.27</v>
+        <v>2.41</v>
       </c>
       <c r="P8" t="n">
-        <v>13.75</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="T8" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1607,43 +1607,43 @@
         <v>8.300000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AB9" t="n">
         <v>1.73</v>
@@ -1652,22 +1652,22 @@
         <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>3.23</v>
+        <v>5.3</v>
       </c>
       <c r="N10" t="n">
+        <v>11</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA10" t="n">
         <v>3.94</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="P10" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.35</v>
+        <v>2.56</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="N11" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG11" t="n">
         <v>2.15</v>
       </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>6.1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>2.97</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>2.34</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="M14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O14" t="n">
         <v>3.7</v>
       </c>
-      <c r="N14" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.51</v>
-      </c>
       <c r="P14" t="n">
-        <v>8</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.28</v>
+        <v>2.93</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="T14" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.95</v>
+        <v>5.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.65</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>1.79</v>
       </c>
       <c r="M16" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="N16" t="n">
         <v>4.2</v>
       </c>
-      <c r="N16" t="n">
-        <v>1.48</v>
-      </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="T16" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="U16" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.33</v>
+        <v>4.65</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="M17" t="n">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="P17" t="n">
-        <v>14.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.56</v>
+        <v>4.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.95</v>
+        <v>4.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.65</v>
+        <v>4.05</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.97</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2.34</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
         <v>2.23</v>
       </c>
       <c r="P18" t="n">
-        <v>8.1</v>
+        <v>2.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.92</v>
+        <v>4.55</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="V18" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.9</v>
+        <v>4.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.13</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.72</v>
+        <v>2.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="AH18" t="n">
-        <v>7.1</v>
+        <v>4.55</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.65</v>
       </c>
-      <c r="M19" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P19" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AD19" t="n">
-        <v>2.41</v>
+        <v>3.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.6</v>
+        <v>1.99</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3059,13 +3059,13 @@
         <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="P20" t="n">
-        <v>12</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.63</v>
+        <v>5.5</v>
       </c>
       <c r="R20" t="n">
         <v>1.29</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>2.72</v>
       </c>
       <c r="M21" t="n">
-        <v>3.85</v>
+        <v>2.58</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3224,16 +3224,16 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3446,28 +3446,28 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>4.25</v>
+        <v>3.85</v>
       </c>
       <c r="N23" t="n">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.48</v>
+        <v>2.1</v>
       </c>
       <c r="P23" t="n">
-        <v>16.75</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="T23" t="n">
         <v>2.32</v>
@@ -3476,10 +3476,10 @@
         <v>1.51</v>
       </c>
       <c r="V23" t="n">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
@@ -3488,31 +3488,31 @@
         <v>11</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC23" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AG23" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AH23" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AI23" t="n">
         <v>1.13</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>6.47</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N27" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V27" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA27" t="n">
         <v>3.85</v>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
       <c r="AB27" t="n">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.61</v>
+        <v>2.09</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.55</v>
+        <v>2.11</v>
       </c>
       <c r="P28" t="n">
-        <v>8.6</v>
+        <v>2.41</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.02</v>
+        <v>4.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="T28" t="n">
-        <v>2.93</v>
+        <v>2.4</v>
       </c>
       <c r="U28" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>7.8</v>
+        <v>5.35</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.02</v>
+        <v>3.92</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.62</v>
+        <v>2.67</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="n">
-        <v>7.3</v>
+        <v>4.7</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>4.55</v>
+        <v>3.85</v>
       </c>
       <c r="O29" t="n">
-        <v>1.53</v>
+        <v>2.08</v>
       </c>
       <c r="P29" t="n">
-        <v>14.75</v>
+        <v>2.16</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.7</v>
+        <v>6.7</v>
       </c>
       <c r="R29" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V29" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z29" t="n">
         <v>1.28</v>
       </c>
-      <c r="S29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V29" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AA29" t="n">
-        <v>3.85</v>
+        <v>3.16</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AC29" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF29" t="n">
         <v>2.09</v>
       </c>
-      <c r="AD29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG29" t="n">
-        <v>2.03</v>
+        <v>1.66</v>
       </c>
       <c r="AH29" t="n">
-        <v>4.8</v>
+        <v>6.85</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4511,13 +4511,13 @@
         <v>5.8</v>
       </c>
       <c r="O31" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
-        <v>11.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="R31" t="n">
         <v>1.31</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M32" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O32" t="n">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>13</v>
+        <v>2.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.9</v>
+        <v>5.25</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S32" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T32" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U32" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V32" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
         <v>13</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH32" t="n">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="N34" t="n">
+        <v>6</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>6</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S34" t="n">
         <v>3.65</v>
       </c>
-      <c r="O34" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P34" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.35</v>
-      </c>
       <c r="T34" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="U34" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="V34" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z34" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y34" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA34" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.91</v>
+        <v>1.46</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AI34" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.05</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5171,43 +5171,43 @@
         <v>3.64</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB36" t="n">
         <v>2.25</v>
@@ -5216,22 +5216,22 @@
         <v>1.53</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="M37" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T37" t="n">
         <v>3.75</v>
       </c>
-      <c r="N37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P37" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U37" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V37" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W37" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="AB37" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG37" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC37" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH37" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,22 +5426,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.03</v>
+        <v>2.56</v>
       </c>
       <c r="M38" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="N38" t="n">
-        <v>3.52</v>
+        <v>2.67</v>
       </c>
       <c r="O38" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="R38" t="n">
         <v>1.53</v>
@@ -5450,10 +5450,10 @@
         <v>2.38</v>
       </c>
       <c r="T38" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U38" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V38" t="n">
         <v>11</v>
@@ -5468,16 +5468,16 @@
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5486,10 +5486,10 @@
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="M39" t="n">
-        <v>2.83</v>
+        <v>3.75</v>
       </c>
       <c r="N39" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="O39" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="R39" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S39" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="U39" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="V39" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.25</v>
+        <v>3.9</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.17</v>
+        <v>2.33</v>
       </c>
       <c r="M3" t="n">
-        <v>7.2</v>
+        <v>3.09</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>2.52</v>
       </c>
       <c r="O3" t="n">
-        <v>1.68</v>
+        <v>2.88</v>
       </c>
       <c r="P3" t="n">
-        <v>2.81</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.31</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.92</v>
+        <v>2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.33</v>
+        <v>1.17</v>
       </c>
       <c r="M4" t="n">
-        <v>3.09</v>
+        <v>7.2</v>
       </c>
       <c r="N4" t="n">
-        <v>2.52</v>
+        <v>12</v>
       </c>
       <c r="O4" t="n">
-        <v>2.88</v>
+        <v>1.68</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.7</v>
+        <v>1.31</v>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>2.92</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
-        <v>3.38</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>3.64</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>2.41</v>
+        <v>1.74</v>
       </c>
       <c r="P8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V8" t="n">
-        <v>7</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD8" t="n">
-        <v>3.35</v>
+        <v>2.56</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.6</v>
+        <v>4.45</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1598,22 +1598,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="N9" t="n">
-        <v>8.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="O9" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="P9" t="n">
         <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R9" t="n">
         <v>1.3</v>
@@ -1628,7 +1628,7 @@
         <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="W9" t="n">
         <v>1.09</v>
@@ -1643,13 +1643,13 @@
         <v>1.19</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD9" t="n">
         <v>2.56</v>
@@ -1658,16 +1658,16 @@
         <v>1.42</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>1.89</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>3.38</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>3.64</v>
       </c>
       <c r="O10" t="n">
-        <v>1.73</v>
+        <v>2.41</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>9.300000000000001</v>
-      </c>
       <c r="Z10" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.65</v>
+        <v>5.8</v>
       </c>
       <c r="M11" t="n">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.15</v>
+        <v>5.85</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.4</v>
+        <v>1.92</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="U11" t="n">
         <v>1.55</v>
       </c>
       <c r="V11" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O12" t="n">
         <v>3.7</v>
       </c>
-      <c r="N12" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.17</v>
-      </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.4</v>
+        <v>2.93</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="T12" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AH12" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,34 +2126,34 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.97</v>
+        <v>1.9</v>
       </c>
       <c r="M13" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.34</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.91</v>
+        <v>6.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
         <v>7.1</v>
@@ -2165,37 +2165,37 @@
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AH13" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
-        <v>3.7</v>
+        <v>2.15</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.93</v>
+        <v>4.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>2.64</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.93</v>
+        <v>2.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V14" t="n">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.88</v>
+        <v>4.45</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.72</v>
+        <v>2.41</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AH14" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.8</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>5.85</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.92</v>
+        <v>5.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="V15" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
         <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="M16" t="n">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>6.1</v>
       </c>
       <c r="O16" t="n">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="P16" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.35</v>
+        <v>6.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>3.18</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>2.38</v>
+        <v>2.84</v>
       </c>
       <c r="U16" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>5.35</v>
+        <v>7.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.95</v>
+        <v>3.08</v>
       </c>
       <c r="AB16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.71</v>
       </c>
-      <c r="AC16" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AH16" t="n">
-        <v>4.65</v>
+        <v>6.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.98</v>
+        <v>2.97</v>
       </c>
       <c r="M17" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O17" t="n">
         <v>3.6</v>
       </c>
-      <c r="N17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.15</v>
-      </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.4</v>
+        <v>2.91</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>2.67</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>5.25</v>
+        <v>7.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>17</v>
+        <v>8.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.65</v>
+        <v>2.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>2.13</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.15</v>
+        <v>1.71</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.3</v>
+        <v>3.72</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.05</v>
+        <v>7.1</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2786,28 +2786,28 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="P18" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="R18" t="n">
         <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="T18" t="n">
         <v>2.38</v>
@@ -2816,7 +2816,7 @@
         <v>1.49</v>
       </c>
       <c r="V18" t="n">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="W18" t="n">
         <v>1.09</v>
@@ -2828,34 +2828,34 @@
         <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.25</v>
+        <v>4.55</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.84</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V19" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.08</v>
+        <v>4.05</v>
       </c>
       <c r="AB19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC19" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AD19" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.99</v>
+        <v>1.66</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="AH19" t="n">
-        <v>6.5</v>
+        <v>4.55</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.48</v>
+        <v>1.98</v>
       </c>
       <c r="M20" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="R20" t="n">
         <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
         <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="W20" t="n">
         <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AA20" t="n">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD20" t="n">
         <v>2.3</v>
       </c>
-      <c r="AD20" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.72</v>
+        <v>1.61</v>
       </c>
       <c r="M21" t="n">
-        <v>2.58</v>
+        <v>4.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.98</v>
+        <v>5.05</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.36</v>
+        <v>2.23</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.25</v>
+        <v>5.5</v>
       </c>
       <c r="M22" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>12</v>
+        <v>1.6</v>
       </c>
       <c r="O22" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC22" t="n">
         <v>1.6</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AD22" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AH22" t="n">
-        <v>7</v>
+        <v>8.1</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O23" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="T23" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="V23" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.45</v>
+        <v>3.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.65</v>
+        <v>2.6</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.11</v>
+        <v>1.47</v>
       </c>
       <c r="AH23" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.5</v>
+        <v>2.72</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="N24" t="n">
-        <v>1.6</v>
+        <v>2.98</v>
       </c>
       <c r="O24" t="n">
-        <v>6.47</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB24" t="n">
         <v>3</v>
       </c>
-      <c r="U24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.23</v>
-      </c>
       <c r="AC24" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AD24" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>4.25</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
         <v>2.1</v>
@@ -3728,10 +3728,10 @@
         <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="T25" t="n">
         <v>2.32</v>
@@ -3740,10 +3740,10 @@
         <v>1.51</v>
       </c>
       <c r="V25" t="n">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
@@ -3752,31 +3752,31 @@
         <v>11</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AG25" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AI25" t="n">
         <v>1.13</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="M26" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
-        <v>2.26</v>
+        <v>2.11</v>
       </c>
       <c r="P26" t="n">
-        <v>2.09</v>
+        <v>2.41</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.93</v>
+        <v>2.4</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="V26" t="n">
-        <v>7.8</v>
+        <v>5.35</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.02</v>
+        <v>3.92</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.62</v>
+        <v>2.67</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>7.3</v>
+        <v>4.7</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="M27" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.55</v>
+        <v>3.85</v>
       </c>
       <c r="O27" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="P27" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.65</v>
+        <v>6.7</v>
       </c>
       <c r="R27" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V27" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z27" t="n">
         <v>1.28</v>
       </c>
-      <c r="S27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V27" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AA27" t="n">
-        <v>3.85</v>
+        <v>3.16</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AC27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF27" t="n">
         <v>2.09</v>
       </c>
-      <c r="AD27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG27" t="n">
-        <v>2.03</v>
+        <v>1.66</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.8</v>
+        <v>6.85</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4106,22 +4106,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N28" t="n">
-        <v>4.1</v>
+        <v>4.55</v>
       </c>
       <c r="O28" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="P28" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="R28" t="n">
         <v>1.28</v>
@@ -4130,16 +4130,16 @@
         <v>3.2</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V28" t="n">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
@@ -4148,34 +4148,34 @@
         <v>9.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.2</v>
+        <v>1.74</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.67</v>
+        <v>2.09</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG28" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="N29" t="n">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="O29" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="P29" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="T29" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="U29" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.89</v>
+        <v>2.09</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.48</v>
+        <v>3.62</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AH29" t="n">
-        <v>6.85</v>
+        <v>7.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="O34" t="n">
-        <v>1.81</v>
+        <v>2.7</v>
       </c>
       <c r="P34" t="n">
-        <v>2.51</v>
+        <v>1.9</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="S34" t="n">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="T34" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="U34" t="n">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="V34" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>17</v>
+        <v>6.25</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="AA34" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.46</v>
+        <v>2.55</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.84</v>
+        <v>9.25</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="N35" t="n">
+        <v>6</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>6</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S35" t="n">
         <v>3.65</v>
       </c>
-      <c r="O35" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.35</v>
-      </c>
       <c r="T35" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="U35" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="V35" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z35" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y35" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA35" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.55</v>
+        <v>1.46</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AI35" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.05</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5162,25 +5162,25 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="M36" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="O36" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="P36" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S36" t="n">
         <v>2.45</v>
@@ -5192,16 +5192,16 @@
         <v>1.29</v>
       </c>
       <c r="V36" t="n">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X36" t="n">
         <v>1.07</v>
       </c>
       <c r="Y36" t="n">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="Z36" t="n">
         <v>1.42</v>
@@ -5210,19 +5210,19 @@
         <v>2.7</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AD36" t="n">
         <v>4.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG36" t="n">
         <v>1.73</v>
@@ -5231,7 +5231,7 @@
         <v>10</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="M37" t="n">
-        <v>2.91</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>3.52</v>
+        <v>2.7</v>
       </c>
       <c r="O37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S37" t="n">
         <v>3</v>
       </c>
-      <c r="P37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.38</v>
-      </c>
       <c r="T37" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="U37" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="V37" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.43</v>
+        <v>1.62</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.49</v>
+        <v>2.18</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,22 +5426,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.56</v>
+        <v>2.03</v>
       </c>
       <c r="M38" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="N38" t="n">
-        <v>2.67</v>
+        <v>3.52</v>
       </c>
       <c r="O38" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P38" t="n">
         <v>1.95</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="R38" t="n">
         <v>1.53</v>
@@ -5450,10 +5450,10 @@
         <v>2.38</v>
       </c>
       <c r="T38" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U38" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V38" t="n">
         <v>11</v>
@@ -5468,16 +5468,16 @@
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5486,10 +5486,10 @@
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V39" t="n">
+        <v>11</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA39" t="n">
         <v>2.25</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V39" t="n">
-        <v>7</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AB39" t="n">
-        <v>1.62</v>
+        <v>2.48</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.18</v>
+        <v>1.47</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AH39" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="M2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="O2" t="n">
         <v>1.2</v>
@@ -722,7 +722,7 @@
         <v>11</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AC2" t="n">
         <v>4.7</v>
@@ -740,10 +740,10 @@
         <v>1.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.33</v>
+        <v>1.15</v>
       </c>
       <c r="M3" t="n">
-        <v>3.09</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>2.52</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>2.88</v>
+        <v>1.68</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>2.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.17</v>
+        <v>2.45</v>
       </c>
       <c r="M4" t="n">
-        <v>7.2</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>2.65</v>
       </c>
       <c r="O4" t="n">
-        <v>1.68</v>
+        <v>2.88</v>
       </c>
       <c r="P4" t="n">
-        <v>2.81</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.31</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.92</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.8</v>
+        <v>1.61</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>1.4</v>
+        <v>6.1</v>
       </c>
       <c r="O11" t="n">
-        <v>5.85</v>
+        <v>2.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.92</v>
+        <v>6.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.35</v>
+        <v>2.84</v>
       </c>
       <c r="U11" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.3</v>
+        <v>3.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.57</v>
+        <v>2.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.23</v>
+        <v>1.78</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.52</v>
+        <v>3.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.55</v>
+        <v>6.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="O12" t="n">
-        <v>3.7</v>
+        <v>5.85</v>
       </c>
       <c r="P12" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.93</v>
+        <v>1.92</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.93</v>
+        <v>2.35</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.88</v>
+        <v>4.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.75</v>
+        <v>2.23</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.72</v>
+        <v>2.52</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AH12" t="n">
-        <v>7.1</v>
+        <v>4.55</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S13" t="n">
         <v>3.3</v>
       </c>
-      <c r="N13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.6</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>5.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.08</v>
+        <v>4.45</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.4</v>
+        <v>2.41</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.99</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="n">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="M14" t="n">
-        <v>4.15</v>
+        <v>3.88</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="T14" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="U14" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="V14" t="n">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.45</v>
+        <v>3.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>2.97</v>
       </c>
       <c r="M15" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>2.34</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.5</v>
+        <v>2.91</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="T15" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="U15" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>8.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.55</v>
+        <v>2.13</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.3</v>
+        <v>1.71</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.45</v>
+        <v>3.72</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.33</v>
+        <v>7.1</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2522,22 +2522,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="R16" t="n">
         <v>1.41</v>
@@ -2570,10 +2570,10 @@
         <v>3.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AD16" t="n">
         <v>3.4</v>
@@ -2582,10 +2582,10 @@
         <v>1.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AH16" t="n">
         <v>6.5</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.97</v>
+        <v>1.48</v>
       </c>
       <c r="M17" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.34</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="P17" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.91</v>
+        <v>5.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>2.67</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.93</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="V17" t="n">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.1</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.13</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.72</v>
+        <v>2.45</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.21</v>
+        <v>1.55</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>7.1</v>
+        <v>4.33</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.88</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
-        <v>2.31</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.35</v>
+        <v>2.93</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3.18</v>
+        <v>2.64</v>
       </c>
       <c r="T18" t="n">
-        <v>2.38</v>
+        <v>2.93</v>
       </c>
       <c r="U18" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>5.35</v>
+        <v>7.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.95</v>
+        <v>2.88</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.62</v>
+        <v>3.72</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.65</v>
+        <v>7.1</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O19" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="P19" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="U19" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="V19" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AA19" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH19" t="n">
         <v>4.05</v>
       </c>
-      <c r="AB19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>4.55</v>
-      </c>
       <c r="AI19" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O20" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.25</v>
       </c>
-      <c r="U20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AD20" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>4.25</v>
+        <v>3.85</v>
       </c>
       <c r="N21" t="n">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>2.1</v>
@@ -3200,10 +3200,10 @@
         <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="T21" t="n">
         <v>2.32</v>
@@ -3212,10 +3212,10 @@
         <v>1.51</v>
       </c>
       <c r="V21" t="n">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
@@ -3224,31 +3224,31 @@
         <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF21" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC21" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AG21" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AH21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AI21" t="n">
         <v>1.13</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5.5</v>
+        <v>2.65</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="N22" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="O22" t="n">
-        <v>6.47</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.23</v>
+        <v>2.99</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
         <v>4.8</v>
       </c>
       <c r="N23" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="O23" t="n">
         <v>1.6</v>
@@ -3494,10 +3494,10 @@
         <v>3.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AD23" t="n">
         <v>3.5</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.72</v>
+        <v>5.9</v>
       </c>
       <c r="M24" t="n">
-        <v>2.58</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>2.98</v>
+        <v>1.55</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>6.47</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="AB24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>4.25</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>5.05</v>
       </c>
       <c r="O25" t="n">
         <v>2.1</v>
@@ -3728,10 +3728,10 @@
         <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S25" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="T25" t="n">
         <v>2.32</v>
@@ -3740,10 +3740,10 @@
         <v>1.51</v>
       </c>
       <c r="V25" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
@@ -3752,31 +3752,31 @@
         <v>11</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AI25" t="n">
         <v>1.13</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="M26" t="n">
         <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="P26" t="n">
-        <v>2.41</v>
+        <v>2.16</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.9</v>
+        <v>6.7</v>
       </c>
       <c r="R26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z26" t="n">
         <v>1.28</v>
       </c>
-      <c r="S26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V26" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AA26" t="n">
-        <v>3.92</v>
+        <v>3.16</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.67</v>
+        <v>3.48</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.72</v>
+        <v>2.09</v>
       </c>
       <c r="AG26" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AH26" t="n">
-        <v>4.7</v>
+        <v>6.85</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
         <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="P27" t="n">
-        <v>2.16</v>
+        <v>2.41</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.7</v>
+        <v>4.9</v>
       </c>
       <c r="R27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V27" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.39</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V27" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AF27" t="n">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="n">
-        <v>6.85</v>
+        <v>4.7</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1</v>
+        <v>3.64</v>
       </c>
       <c r="N28" t="n">
-        <v>4.55</v>
+        <v>5.4</v>
       </c>
       <c r="O28" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="P28" t="n">
-        <v>2.38</v>
+        <v>2.09</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.65</v>
+        <v>5.8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.42</v>
+        <v>2.93</v>
       </c>
       <c r="U28" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
-        <v>5.45</v>
+        <v>7.8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.85</v>
+        <v>3.02</v>
       </c>
       <c r="AB28" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC28" t="n">
         <v>1.74</v>
       </c>
-      <c r="AC28" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AD28" t="n">
-        <v>2.7</v>
+        <v>3.62</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.03</v>
+        <v>1.73</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.8</v>
+        <v>7.3</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="M29" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>5.4</v>
+        <v>4.55</v>
       </c>
       <c r="O29" t="n">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="P29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V29" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC29" t="n">
         <v>2.09</v>
       </c>
-      <c r="Q29" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AD29" t="n">
-        <v>3.62</v>
+        <v>2.7</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.73</v>
+        <v>2.03</v>
       </c>
       <c r="AH29" t="n">
-        <v>7.3</v>
+        <v>4.8</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="M31" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="O31" t="n">
         <v>2</v>
@@ -4538,10 +4538,10 @@
         <v>1.12</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z31" t="n">
         <v>1.18</v>
@@ -4550,10 +4550,10 @@
         <v>4.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD31" t="n">
         <v>2.6</v>
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="O32" t="n">
         <v>2</v>
@@ -4670,10 +4670,10 @@
         <v>1.12</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z32" t="n">
         <v>1.18</v>
@@ -4682,10 +4682,10 @@
         <v>4.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AD32" t="n">
         <v>2.6</v>
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="N34" t="n">
+        <v>6</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>6</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S34" t="n">
         <v>3.65</v>
       </c>
-      <c r="O34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.35</v>
-      </c>
       <c r="T34" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="U34" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="V34" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z34" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y34" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA34" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.55</v>
+        <v>1.46</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AI34" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.05</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="O35" t="n">
-        <v>1.81</v>
+        <v>2.7</v>
       </c>
       <c r="P35" t="n">
-        <v>2.51</v>
+        <v>1.9</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="R35" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="S35" t="n">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="T35" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="V35" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>17</v>
+        <v>6.25</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="AA35" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.46</v>
+        <v>2.55</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AH35" t="n">
-        <v>3.84</v>
+        <v>9.25</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V37" t="n">
+        <v>11</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA37" t="n">
         <v>2.25</v>
       </c>
-      <c r="M37" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V37" t="n">
-        <v>7</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AB37" t="n">
-        <v>1.62</v>
+        <v>2.48</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.18</v>
+        <v>1.47</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AH37" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="M38" t="n">
-        <v>2.91</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>3.52</v>
+        <v>2.7</v>
       </c>
       <c r="O38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S38" t="n">
         <v>3</v>
       </c>
-      <c r="P38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.38</v>
-      </c>
       <c r="T38" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="U38" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="V38" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W38" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.43</v>
+        <v>1.62</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.49</v>
+        <v>2.18</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,22 +5558,22 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.56</v>
+        <v>2.03</v>
       </c>
       <c r="M39" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="N39" t="n">
-        <v>2.67</v>
+        <v>3.52</v>
       </c>
       <c r="O39" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
         <v>1.95</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="R39" t="n">
         <v>1.53</v>
@@ -5582,10 +5582,10 @@
         <v>2.38</v>
       </c>
       <c r="T39" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U39" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V39" t="n">
         <v>11</v>
@@ -5600,16 +5600,16 @@
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5618,10 +5618,10 @@
         <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH39" t="n">
         <v>0</v>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>7.26</v>
+        <v>6.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.98</v>
@@ -1097,7 +1097,7 @@
         <v>2.72</v>
       </c>
       <c r="U5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V5" t="n">
         <v>6.7</v>
@@ -1118,16 +1118,16 @@
         <v>3.22</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC5" t="n">
         <v>1.86</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF5" t="n">
         <v>2.03</v>
@@ -1136,7 +1136,7 @@
         <v>1.69</v>
       </c>
       <c r="AH5" t="n">
-        <v>5.65</v>
+        <v>5.8</v>
       </c>
       <c r="AI5" t="n">
         <v>1.08</v>
@@ -1202,34 +1202,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="S6" t="n">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="T6" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V6" t="n">
         <v>7.8</v>
@@ -1241,34 +1241,34 @@
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH6" t="n">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="AI6" t="n">
         <v>1.03</v>
@@ -1340,70 +1340,70 @@
         <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O7" t="n">
         <v>2.74</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="U7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.29</v>
+        <v>1.89</v>
       </c>
       <c r="M9" t="n">
-        <v>5.3</v>
+        <v>3.38</v>
       </c>
       <c r="N9" t="n">
-        <v>11</v>
+        <v>3.64</v>
       </c>
       <c r="O9" t="n">
-        <v>1.73</v>
+        <v>2.41</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>9.300000000000001</v>
-      </c>
       <c r="Z9" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.89</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>3.38</v>
+        <v>5.3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.64</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
-        <v>2.41</v>
+        <v>1.73</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>2.77</v>
+        <v>3.08</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.1</v>
+        <v>3.94</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.35</v>
+        <v>2.56</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O11" t="n">
         <v>3.7</v>
       </c>
-      <c r="N11" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.17</v>
-      </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.4</v>
+        <v>2.93</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="T11" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="U11" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>5.85</v>
+        <v>2.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.92</v>
+        <v>6.25</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.35</v>
+        <v>2.84</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.3</v>
+        <v>3.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.23</v>
+        <v>1.65</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.52</v>
+        <v>3.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.55</v>
+        <v>6.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.65</v>
       </c>
-      <c r="M13" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="AC13" t="n">
         <v>2.25</v>
       </c>
-      <c r="U13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AD13" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="M14" t="n">
-        <v>3.88</v>
+        <v>4.15</v>
       </c>
       <c r="N14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH14" t="n">
         <v>4.2</v>
       </c>
-      <c r="O14" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>4.65</v>
-      </c>
       <c r="AI14" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.97</v>
+        <v>1.79</v>
       </c>
       <c r="M15" t="n">
-        <v>3.44</v>
+        <v>3.88</v>
       </c>
       <c r="N15" t="n">
-        <v>2.34</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>2.31</v>
       </c>
       <c r="P15" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.91</v>
+        <v>4.35</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>2.67</v>
+        <v>3.18</v>
       </c>
       <c r="T15" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="V15" t="n">
-        <v>7.1</v>
+        <v>5.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
         <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC15" t="n">
         <v>2.13</v>
       </c>
-      <c r="AC15" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AD15" t="n">
-        <v>3.72</v>
+        <v>2.62</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>7.1</v>
+        <v>4.65</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2522,22 +2522,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N16" t="n">
-        <v>4.5</v>
+        <v>6.1</v>
       </c>
       <c r="O16" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="P16" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="R16" t="n">
         <v>1.41</v>
@@ -2570,10 +2570,10 @@
         <v>3.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AD16" t="n">
         <v>3.4</v>
@@ -2582,10 +2582,10 @@
         <v>1.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AH16" t="n">
         <v>6.5</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>5.85</v>
       </c>
       <c r="P18" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.93</v>
+        <v>1.92</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.93</v>
+        <v>2.35</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V18" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.88</v>
+        <v>4.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>2.23</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.72</v>
+        <v>2.52</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AH18" t="n">
-        <v>7.1</v>
+        <v>4.55</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.98</v>
+        <v>2.97</v>
       </c>
       <c r="M19" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O19" t="n">
         <v>3.6</v>
       </c>
-      <c r="N19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.15</v>
-      </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.4</v>
+        <v>2.91</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>2.67</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="U19" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>5.25</v>
+        <v>7.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>17</v>
+        <v>8.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.65</v>
+        <v>2.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>2.13</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.15</v>
+        <v>1.71</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.3</v>
+        <v>3.72</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.05</v>
+        <v>7.1</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="P20" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="V20" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AA20" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH20" t="n">
         <v>4.05</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>4.55</v>
-      </c>
       <c r="AI20" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="T21" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="V21" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.45</v>
+        <v>3.4</v>
       </c>
       <c r="AB21" t="n">
         <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.65</v>
+        <v>2.6</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.11</v>
+        <v>1.47</v>
       </c>
       <c r="AH21" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.65</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>2.8</v>
+        <v>3.85</v>
       </c>
       <c r="N22" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.4</v>
+        <v>4.45</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.99</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O23" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.3</v>
       </c>
-      <c r="M23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N23" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.35</v>
-      </c>
       <c r="V23" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.300000000000001</v>
+        <v>6.65</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AH23" t="n">
-        <v>7</v>
+        <v>8.1</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.9</v>
+        <v>2.65</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="N24" t="n">
-        <v>1.55</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
-        <v>6.47</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>2</v>
+        <v>2.99</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="AD24" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="O27" t="n">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="P27" t="n">
-        <v>2.41</v>
+        <v>2.09</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T27" t="n">
-        <v>2.4</v>
+        <v>2.93</v>
       </c>
       <c r="U27" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>5.35</v>
+        <v>7.8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.92</v>
+        <v>3.02</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.67</v>
+        <v>3.62</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="AG27" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.7</v>
+        <v>7.3</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="M28" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="N28" t="n">
-        <v>5.4</v>
+        <v>4.55</v>
       </c>
       <c r="O28" t="n">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="P28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2.09</v>
       </c>
-      <c r="Q28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AD28" t="n">
-        <v>3.62</v>
+        <v>2.7</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.73</v>
+        <v>2.03</v>
       </c>
       <c r="AH28" t="n">
-        <v>7.3</v>
+        <v>4.8</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4238,22 +4238,22 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="M29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N29" t="n">
         <v>4.1</v>
       </c>
-      <c r="N29" t="n">
-        <v>4.55</v>
-      </c>
       <c r="O29" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="P29" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="R29" t="n">
         <v>1.28</v>
@@ -4262,16 +4262,16 @@
         <v>3.2</v>
       </c>
       <c r="T29" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U29" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>5.45</v>
+        <v>5.35</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
@@ -4280,34 +4280,34 @@
         <v>9.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.09</v>
+        <v>1.67</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="M32" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="O32" t="n">
         <v>2</v>
@@ -4670,10 +4670,10 @@
         <v>1.12</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z32" t="n">
         <v>1.18</v>
@@ -4682,10 +4682,10 @@
         <v>4.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD32" t="n">
         <v>2.6</v>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="M33" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="N33" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="O33" t="n">
         <v>2</v>
       </c>
       <c r="P33" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="R33" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S33" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U33" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X33" t="n">
         <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH33" t="n">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -5174,10 +5174,10 @@
         <v>2.77</v>
       </c>
       <c r="P36" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>4.63</v>
       </c>
       <c r="R36" t="n">
         <v>1.5</v>
@@ -5201,7 +5201,7 @@
         <v>1.07</v>
       </c>
       <c r="Y36" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="Z36" t="n">
         <v>1.42</v>
@@ -5219,7 +5219,7 @@
         <v>4.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF36" t="n">
         <v>2</v>
@@ -5231,7 +5231,7 @@
         <v>10</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="M37" t="n">
-        <v>2.83</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="O37" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P37" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R37" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S37" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="U37" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="V37" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.25</v>
+        <v>3.9</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.48</v>
+        <v>1.62</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="M38" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T38" t="n">
         <v>3.75</v>
       </c>
-      <c r="N38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U38" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V38" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W38" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="AB38" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG38" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC38" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH38" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,22 +5558,22 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.03</v>
+        <v>2.56</v>
       </c>
       <c r="M39" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="N39" t="n">
-        <v>3.52</v>
+        <v>2.67</v>
       </c>
       <c r="O39" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P39" t="n">
         <v>1.95</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
         <v>1.53</v>
@@ -5582,10 +5582,10 @@
         <v>2.38</v>
       </c>
       <c r="T39" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U39" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V39" t="n">
         <v>11</v>
@@ -5600,16 +5600,16 @@
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5618,10 +5618,10 @@
         <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH39" t="n">
         <v>0</v>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -683,13 +683,13 @@
         <v>38</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
         <v>1.09</v>
@@ -815,13 +815,13 @@
         <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>1.68</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
         <v>1.17</v>
@@ -947,13 +947,13 @@
         <v>2.65</v>
       </c>
       <c r="O4" t="n">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1070,22 +1070,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="N5" t="n">
-        <v>6.25</v>
+        <v>8.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.55</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
         <v>1.38</v>
@@ -1118,10 +1118,10 @@
         <v>3.22</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AD5" t="n">
         <v>3</v>
@@ -1205,19 +1205,19 @@
         <v>3.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="R6" t="n">
         <v>1.37</v>
@@ -1250,10 +1250,10 @@
         <v>3.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AD6" t="n">
         <v>3.5</v>
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.74</v>
+        <v>1.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
         <v>1.45</v>
@@ -1382,10 +1382,10 @@
         <v>3</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AD7" t="n">
         <v>3.6</v>
@@ -1466,22 +1466,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="N8" t="n">
-        <v>8.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="O8" t="n">
-        <v>1.74</v>
+        <v>1.27</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>13.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.4</v>
+        <v>4.3</v>
       </c>
       <c r="R8" t="n">
         <v>1.3</v>
@@ -1496,7 +1496,7 @@
         <v>1.49</v>
       </c>
       <c r="V8" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="W8" t="n">
         <v>1.09</v>
@@ -1511,13 +1511,13 @@
         <v>1.19</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
         <v>2.56</v>
@@ -1526,16 +1526,16 @@
         <v>1.42</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.38</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>3.64</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>2.41</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V9" t="n">
-        <v>7</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD9" t="n">
-        <v>3.35</v>
+        <v>2.56</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.6</v>
+        <v>4.45</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>1.89</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>3.38</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>3.64</v>
       </c>
       <c r="O10" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>9.300000000000001</v>
-      </c>
       <c r="Z10" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>1.51</v>
       </c>
       <c r="O11" t="n">
-        <v>3.7</v>
+        <v>3.02</v>
       </c>
       <c r="P11" t="n">
-        <v>2.08</v>
+        <v>16.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.93</v>
+        <v>1.38</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.64</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.93</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V11" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AA11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD11" t="n">
         <v>2.88</v>
       </c>
-      <c r="AB11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.72</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AF11" t="n">
         <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AH11" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="M12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P12" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S12" t="n">
         <v>3.3</v>
       </c>
-      <c r="N12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.6</v>
-      </c>
       <c r="T12" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>7.1</v>
+        <v>5.25</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.08</v>
+        <v>4.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.99</v>
+        <v>1.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AH12" t="n">
-        <v>6.5</v>
+        <v>4.05</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.35</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.55</v>
+        <v>1.93</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="T13" t="n">
-        <v>2.38</v>
+        <v>2.93</v>
       </c>
       <c r="U13" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.05</v>
+        <v>2.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.6</v>
+        <v>3.72</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.55</v>
+        <v>7.1</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC14" t="n">
         <v>1.65</v>
       </c>
-      <c r="M14" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AD14" t="n">
-        <v>2.41</v>
+        <v>3.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.6</v>
+        <v>1.99</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.88</v>
+        <v>4.15</v>
       </c>
       <c r="N15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P15" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH15" t="n">
         <v>4.2</v>
       </c>
-      <c r="O15" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>4.65</v>
-      </c>
       <c r="AI15" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>6.1</v>
+        <v>3.65</v>
       </c>
       <c r="O16" t="n">
-        <v>2.17</v>
+        <v>1.54</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>15</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.4</v>
+        <v>2.66</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.84</v>
+        <v>2.38</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V16" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.08</v>
+        <v>4.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.71</v>
+        <v>2.09</v>
       </c>
       <c r="AH16" t="n">
-        <v>6.5</v>
+        <v>4.55</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="M17" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="O17" t="n">
-        <v>2.05</v>
+        <v>1.51</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.5</v>
+        <v>3.28</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.84</v>
       </c>
       <c r="U17" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>5</v>
+        <v>3.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>2.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.8</v>
+        <v>2.97</v>
       </c>
       <c r="M18" t="n">
-        <v>4.3</v>
+        <v>3.44</v>
       </c>
       <c r="N18" t="n">
-        <v>1.4</v>
+        <v>2.34</v>
       </c>
       <c r="O18" t="n">
-        <v>5.85</v>
+        <v>2.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.35</v>
+        <v>8.1</v>
       </c>
       <c r="Q18" t="n">
         <v>1.92</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="T18" t="n">
-        <v>2.35</v>
+        <v>2.93</v>
       </c>
       <c r="U18" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>8.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.57</v>
+        <v>2.13</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.23</v>
+        <v>1.71</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.52</v>
+        <v>3.72</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.55</v>
+        <v>7.1</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.97</v>
+        <v>1.79</v>
       </c>
       <c r="M19" t="n">
-        <v>3.44</v>
+        <v>3.88</v>
       </c>
       <c r="N19" t="n">
-        <v>2.34</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>1.58</v>
       </c>
       <c r="P19" t="n">
-        <v>2.12</v>
+        <v>14.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.91</v>
+        <v>2.56</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>2.67</v>
+        <v>3.18</v>
       </c>
       <c r="T19" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="V19" t="n">
-        <v>7.1</v>
+        <v>5.35</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="AB19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.13</v>
       </c>
-      <c r="AC19" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AD19" t="n">
-        <v>3.72</v>
+        <v>2.62</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>7.1</v>
+        <v>4.65</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.98</v>
+        <v>1.48</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>12</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.4</v>
+        <v>2.63</v>
       </c>
       <c r="R20" t="n">
         <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
         <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W20" t="n">
         <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
         <v>1.3</v>
       </c>
-      <c r="M21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N21" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.35</v>
-      </c>
       <c r="V21" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>8.300000000000001</v>
+        <v>6.65</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AH21" t="n">
-        <v>7</v>
+        <v>8.1</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="O22" t="n">
-        <v>2.1</v>
+        <v>1.26</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>9</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="U22" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="V22" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.45</v>
+        <v>3.4</v>
       </c>
       <c r="AB22" t="n">
         <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.65</v>
+        <v>2.6</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.11</v>
+        <v>1.47</v>
       </c>
       <c r="AH22" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5.9</v>
+        <v>2.65</v>
       </c>
       <c r="M23" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="N23" t="n">
-        <v>1.55</v>
+        <v>2.9</v>
       </c>
       <c r="O23" t="n">
-        <v>6.47</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>2</v>
+        <v>2.99</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.65</v>
+        <v>1.61</v>
       </c>
       <c r="M24" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P24" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="Q24" t="n">
         <v>2.8</v>
       </c>
-      <c r="N24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.99</v>
+        <v>1.65</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.34</v>
+        <v>2.23</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3710,28 +3710,28 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>4.25</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>17</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="T25" t="n">
         <v>2.32</v>
@@ -3740,10 +3740,10 @@
         <v>1.51</v>
       </c>
       <c r="V25" t="n">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
@@ -3752,31 +3752,31 @@
         <v>11</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AG25" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AI25" t="n">
         <v>1.13</v>
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="O26" t="n">
-        <v>2.08</v>
+        <v>1.55</v>
       </c>
       <c r="P26" t="n">
-        <v>2.16</v>
+        <v>8.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.7</v>
+        <v>3.02</v>
       </c>
       <c r="R26" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="U26" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.89</v>
+        <v>2.09</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.48</v>
+        <v>3.62</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AH26" t="n">
-        <v>6.85</v>
+        <v>7.3</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="M27" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="N27" t="n">
-        <v>5.4</v>
+        <v>4.55</v>
       </c>
       <c r="O27" t="n">
-        <v>2.26</v>
+        <v>1.53</v>
       </c>
       <c r="P27" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V27" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC27" t="n">
         <v>2.09</v>
       </c>
-      <c r="Q27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AD27" t="n">
-        <v>3.62</v>
+        <v>2.7</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.73</v>
+        <v>2.03</v>
       </c>
       <c r="AH27" t="n">
-        <v>7.3</v>
+        <v>4.8</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>4.55</v>
+        <v>3.85</v>
       </c>
       <c r="O28" t="n">
-        <v>2.19</v>
+        <v>1.44</v>
       </c>
       <c r="P28" t="n">
-        <v>2.38</v>
+        <v>9</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.65</v>
+        <v>3.46</v>
       </c>
       <c r="R28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V28" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z28" t="n">
         <v>1.28</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V28" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AA28" t="n">
-        <v>3.85</v>
+        <v>3.16</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AC28" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF28" t="n">
         <v>2.09</v>
       </c>
-      <c r="AD28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG28" t="n">
-        <v>2.03</v>
+        <v>1.66</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.8</v>
+        <v>6.85</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4247,13 +4247,13 @@
         <v>4.1</v>
       </c>
       <c r="O29" t="n">
-        <v>2.11</v>
+        <v>1.49</v>
       </c>
       <c r="P29" t="n">
-        <v>2.41</v>
+        <v>15.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.9</v>
+        <v>2.81</v>
       </c>
       <c r="R29" t="n">
         <v>1.28</v>
@@ -4379,13 +4379,13 @@
         <v>4.7</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="P30" t="n">
-        <v>2.4</v>
+        <v>13</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="R30" t="n">
         <v>1.28</v>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4643,13 +4643,13 @@
         <v>5</v>
       </c>
       <c r="O32" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="P32" t="n">
-        <v>2.3</v>
+        <v>11.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.25</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
         <v>1.31</v>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="O34" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="P34" t="n">
-        <v>2.51</v>
+        <v>6.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="S34" t="n">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="T34" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="U34" t="n">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="V34" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>17</v>
+        <v>6.25</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="AA34" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.46</v>
+        <v>2.55</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.84</v>
+        <v>9.25</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="N35" t="n">
+        <v>6</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P35" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S35" t="n">
         <v>3.65</v>
       </c>
-      <c r="O35" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.35</v>
-      </c>
       <c r="T35" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="U35" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="V35" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z35" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y35" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA35" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.55</v>
+        <v>1.46</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AI35" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.05</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5162,22 +5162,22 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="N36" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="O36" t="n">
-        <v>2.77</v>
+        <v>1.73</v>
       </c>
       <c r="P36" t="n">
-        <v>1.95</v>
+        <v>7</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.63</v>
+        <v>2.4</v>
       </c>
       <c r="R36" t="n">
         <v>1.5</v>
@@ -5210,10 +5210,10 @@
         <v>2.7</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AD36" t="n">
         <v>4.5</v>
@@ -5303,13 +5303,13 @@
         <v>2.7</v>
       </c>
       <c r="O37" t="n">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="P37" t="n">
-        <v>2.25</v>
+        <v>11.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="R37" t="n">
         <v>1.36</v>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,22 +5426,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.03</v>
+        <v>2.56</v>
       </c>
       <c r="M38" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="N38" t="n">
-        <v>3.52</v>
+        <v>2.67</v>
       </c>
       <c r="O38" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="P38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.5</v>
+        <v>2.05</v>
       </c>
       <c r="R38" t="n">
         <v>1.53</v>
@@ -5450,10 +5450,10 @@
         <v>2.38</v>
       </c>
       <c r="T38" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U38" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V38" t="n">
         <v>11</v>
@@ -5468,16 +5468,16 @@
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5486,10 +5486,10 @@
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,22 +5558,22 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.56</v>
+        <v>2.03</v>
       </c>
       <c r="M39" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="N39" t="n">
-        <v>2.67</v>
+        <v>3.52</v>
       </c>
       <c r="O39" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="P39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="R39" t="n">
         <v>1.53</v>
@@ -5582,10 +5582,10 @@
         <v>2.38</v>
       </c>
       <c r="T39" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U39" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V39" t="n">
         <v>11</v>
@@ -5600,16 +5600,16 @@
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5618,10 +5618,10 @@
         <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH39" t="n">
         <v>0</v>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL39"/>
+  <dimension ref="A1:AL36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.15</v>
+        <v>2.45</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>14</v>
+        <v>2.65</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.45</v>
+        <v>1.15</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="N4" t="n">
-        <v>2.65</v>
+        <v>14</v>
       </c>
       <c r="O4" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1029,27 +1029,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,52 +1070,52 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="M5" t="n">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="N5" t="n">
-        <v>8.5</v>
+        <v>3.64</v>
       </c>
       <c r="O5" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="T5" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="U5" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AB5" t="n">
         <v>1.95</v>
@@ -1124,22 +1124,22 @@
         <v>1.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>45881.42708333334</v>
+        <v>45881.54166666666</v>
       </c>
     </row>
     <row r="6">
@@ -1161,27 +1161,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="N6" t="n">
-        <v>2.16</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>2.4</v>
+        <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.73</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AC6" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.5</v>
+        <v>2.56</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="AH6" t="n">
-        <v>6.5</v>
+        <v>4.45</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>45881.45833333334</v>
+        <v>45881.54166666666</v>
       </c>
     </row>
     <row r="7">
@@ -1293,27 +1293,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.12</v>
+        <v>1.29</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="O7" t="n">
-        <v>1.8</v>
+        <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>13.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V7" t="n">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AA7" t="n">
-        <v>3</v>
+        <v>3.94</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.69</v>
+        <v>2.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.6</v>
+        <v>2.56</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AH7" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>45881.52083333334</v>
+        <v>45881.54166666666</v>
       </c>
     </row>
     <row r="8">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,28 +1466,28 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.29</v>
+        <v>1.79</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3</v>
+        <v>3.88</v>
       </c>
       <c r="N8" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="P8" t="n">
-        <v>13.75</v>
+        <v>14.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.3</v>
+        <v>2.56</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="T8" t="n">
         <v>2.38</v>
@@ -1496,46 +1496,46 @@
         <v>1.49</v>
       </c>
       <c r="V8" t="n">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="W8" t="n">
         <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
         <v>1.19</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.14</v>
+        <v>1.64</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.63</v>
+        <v>2.12</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>45881.54166666666</v>
+        <v>45881.58333333334</v>
       </c>
     </row>
     <row r="9">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.4</v>
       </c>
-      <c r="M9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N9" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P9" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.3</v>
-      </c>
       <c r="S9" t="n">
-        <v>3.08</v>
+        <v>2.64</v>
       </c>
       <c r="T9" t="n">
-        <v>2.38</v>
+        <v>2.93</v>
       </c>
       <c r="U9" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.98</v>
+        <v>2.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.56</v>
+        <v>3.72</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.45</v>
+        <v>7.1</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45881.54166666666</v>
+        <v>45881.58333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="N10" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="P10" t="n">
-        <v>8.699999999999999</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.6</v>
+        <v>4.55</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45881.54166666666</v>
+        <v>45881.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.1</v>
+        <v>1.98</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>1.51</v>
+        <v>3.7</v>
       </c>
       <c r="O11" t="n">
-        <v>3.02</v>
+        <v>1.53</v>
       </c>
       <c r="P11" t="n">
-        <v>16.25</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.38</v>
+        <v>2.65</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
         <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
         <v>1.55</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.5</v>
+        <v>4.65</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.3</v>
+        <v>4.05</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.98</v>
+        <v>2.97</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7</v>
+        <v>2.34</v>
       </c>
       <c r="O12" t="n">
-        <v>1.53</v>
+        <v>2.23</v>
       </c>
       <c r="P12" t="n">
-        <v>12</v>
+        <v>8.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.65</v>
+        <v>1.92</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>2.67</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>5.25</v>
+        <v>7.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>17</v>
+        <v>8.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.65</v>
+        <v>2.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>2.13</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.15</v>
+        <v>1.71</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.3</v>
+        <v>3.72</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.05</v>
+        <v>7.1</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="O13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.25</v>
       </c>
-      <c r="P13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.93</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.88</v>
+        <v>4.45</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.72</v>
+        <v>2.41</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>5.1</v>
       </c>
       <c r="M15" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="N15" t="n">
-        <v>4.8</v>
+        <v>1.51</v>
       </c>
       <c r="O15" t="n">
-        <v>1.53</v>
+        <v>3.02</v>
       </c>
       <c r="P15" t="n">
-        <v>12</v>
+        <v>16.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.65</v>
+        <v>1.38</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
         <v>3.3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
         <v>1.55</v>
       </c>
       <c r="V15" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="P16" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="V16" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z16" t="n">
         <v>1.18</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.97</v>
+        <v>1.85</v>
       </c>
       <c r="M18" t="n">
-        <v>3.44</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>2.34</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.23</v>
+        <v>1.48</v>
       </c>
       <c r="P18" t="n">
-        <v>8.1</v>
+        <v>17</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.92</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>2.67</v>
+        <v>3.42</v>
       </c>
       <c r="T18" t="n">
-        <v>2.93</v>
+        <v>2.32</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="V18" t="n">
-        <v>7.1</v>
+        <v>5.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.1</v>
+        <v>11</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.9</v>
+        <v>4.45</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.72</v>
+        <v>2.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="AH18" t="n">
-        <v>7.1</v>
+        <v>4.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="AL18" s="3" t="n">
-        <v>45881.58333333334</v>
+        <v>45881.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="M19" t="n">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="N19" t="n">
-        <v>4.2</v>
+        <v>5.05</v>
       </c>
       <c r="O19" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="P19" t="n">
-        <v>14.5</v>
+        <v>16.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S19" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="T19" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="U19" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="V19" t="n">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="AL19" s="3" t="n">
-        <v>45881.58333333334</v>
+        <v>45881.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -3009,27 +3009,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.48</v>
+        <v>2.65</v>
       </c>
       <c r="M20" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.5</v>
       </c>
-      <c r="P20" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AA20" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.55</v>
+        <v>2.99</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>1.34</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="AL20" s="3" t="n">
-        <v>45881.58333333334</v>
+        <v>45881.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.65</v>
+        <v>1.69</v>
       </c>
       <c r="M23" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.9</v>
+        <v>4.55</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>14.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.4</v>
+        <v>3.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.99</v>
+        <v>1.74</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.34</v>
+        <v>2.09</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>45881.60416666666</v>
+        <v>45881.63541666666</v>
       </c>
     </row>
     <row r="24">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="M24" t="n">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>5.05</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P24" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.48</v>
       </c>
-      <c r="P24" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.51</v>
-      </c>
       <c r="V24" t="n">
-        <v>5.45</v>
+        <v>5.35</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.4</v>
+        <v>3.92</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.23</v>
+        <v>1.67</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="AL24" s="3" t="n">
-        <v>45881.60416666666</v>
+        <v>45881.63541666666</v>
       </c>
     </row>
     <row r="25">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>3.64</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="O25" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="P25" t="n">
-        <v>17</v>
+        <v>8.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>3.42</v>
+        <v>2.6</v>
       </c>
       <c r="T25" t="n">
-        <v>2.32</v>
+        <v>2.93</v>
       </c>
       <c r="U25" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.45</v>
+        <v>3.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.5</v>
+        <v>3.62</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.65</v>
+        <v>1.99</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.11</v>
+        <v>1.73</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.5</v>
+        <v>7.3</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="AL25" s="3" t="n">
-        <v>45881.60416666666</v>
+        <v>45881.63541666666</v>
       </c>
     </row>
     <row r="26">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="M26" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>5.4</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.02</v>
+        <v>3.46</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="T26" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V26" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.02</v>
+        <v>3.16</v>
       </c>
       <c r="AB26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF26" t="n">
         <v>2.09</v>
       </c>
-      <c r="AC26" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AH26" t="n">
-        <v>7.3</v>
+        <v>6.85</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="M27" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="N27" t="n">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="O27" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="P27" t="n">
-        <v>14.75</v>
+        <v>13</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R27" t="n">
         <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="U27" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="V27" t="n">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>9.1</v>
+        <v>13</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="AL27" s="3" t="n">
-        <v>45881.63541666666</v>
+        <v>45881.66666666666</v>
       </c>
     </row>
     <row r="28">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="AL28" s="3" t="n">
-        <v>45881.63541666666</v>
+        <v>45881.66666666666</v>
       </c>
     </row>
     <row r="29">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,73 +4238,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="P29" t="n">
-        <v>15.25</v>
+        <v>11.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S29" t="n">
         <v>3.2</v>
       </c>
       <c r="T29" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V29" t="n">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.1</v>
+        <v>13</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.92</v>
+        <v>4.05</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AG29" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH29" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AI29" t="n">
         <v>1.12</v>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="AL29" s="3" t="n">
-        <v>45881.63541666666</v>
+        <v>45881.66666666666</v>
       </c>
     </row>
     <row r="30">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="M30" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="N30" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="O30" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P30" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S30" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T30" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U30" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V30" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X30" t="n">
         <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4461,27 +4461,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,37 +4502,37 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="M31" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="N31" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O31" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="P31" t="n">
-        <v>11.5</v>
+        <v>19.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="R31" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="T31" t="n">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="U31" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="V31" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W31" t="n">
         <v>1.12</v>
@@ -4541,38 +4541,38 @@
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Z31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AI31" t="n">
         <v>1.18</v>
       </c>
-      <c r="AA31" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AJ31" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="AL31" s="3" t="n">
-        <v>45881.66666666666</v>
+        <v>45881.79166666666</v>
       </c>
     </row>
     <row r="32">
@@ -4593,27 +4593,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="O32" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="P32" t="n">
-        <v>11.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="R32" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="S32" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="T32" t="n">
-        <v>2.37</v>
+        <v>3.3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="V32" t="n">
-        <v>5.5</v>
+        <v>9.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>13</v>
+        <v>6.25</v>
       </c>
       <c r="Z32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1.18</v>
       </c>
-      <c r="AA32" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AF32" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AH32" t="n">
-        <v>4.65</v>
+        <v>9.25</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="AL32" s="3" t="n">
-        <v>45881.66666666666</v>
+        <v>45881.79166666666</v>
       </c>
     </row>
     <row r="33">
@@ -4725,27 +4725,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="AL33" s="3" t="n">
-        <v>45881.66666666666</v>
+        <v>45881.8125</v>
       </c>
     </row>
     <row r="34">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="N34" t="n">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="O34" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="P34" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="R34" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S34" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="T34" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="U34" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V34" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="W34" t="n">
         <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
         <v>1.55</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH34" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="AL34" s="3" t="n">
-        <v>45881.79166666666</v>
+        <v>45881.89583333334</v>
       </c>
     </row>
     <row r="35">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.42</v>
+        <v>2.56</v>
       </c>
       <c r="M35" t="n">
-        <v>4.9</v>
+        <v>2.83</v>
       </c>
       <c r="N35" t="n">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="O35" t="n">
-        <v>1.32</v>
+        <v>2.05</v>
       </c>
       <c r="P35" t="n">
-        <v>19.75</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.24</v>
+        <v>2.05</v>
       </c>
       <c r="R35" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="S35" t="n">
-        <v>3.65</v>
+        <v>2.38</v>
       </c>
       <c r="T35" t="n">
-        <v>2.23</v>
+        <v>3.5</v>
       </c>
       <c r="U35" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="V35" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="W35" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.1</v>
+        <v>1.53</v>
       </c>
       <c r="AA35" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.46</v>
+        <v>2.48</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.38</v>
+        <v>1.47</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AH35" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="AL35" s="3" t="n">
-        <v>45881.79166666666</v>
+        <v>45881.89583333334</v>
       </c>
     </row>
     <row r="36">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,76 +5162,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="M36" t="n">
-        <v>3.06</v>
+        <v>3.75</v>
       </c>
       <c r="N36" t="n">
-        <v>3.64</v>
+        <v>2.7</v>
       </c>
       <c r="O36" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="P36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V36" t="n">
         <v>7</v>
       </c>
-      <c r="Q36" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V36" t="n">
-        <v>8.5</v>
-      </c>
       <c r="W36" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X36" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Z36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE36" t="n">
         <v>1.42</v>
       </c>
-      <c r="AA36" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AF36" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AH36" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5244,402 +5244,6 @@
         </is>
       </c>
       <c r="AL36" s="3" t="n">
-        <v>45881.8125</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>45881</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Wilstermann</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="M37" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P37" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V37" t="n">
-        <v>7</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL37" s="3" t="n">
-        <v>45881.89583333334</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>45881</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Peñarol</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Racing Club</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="M38" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="O38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V38" t="n">
-        <v>11</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL38" s="3" t="n">
-        <v>45881.89583333334</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>45881</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Atlético Nacional</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="M39" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V39" t="n">
-        <v>11</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL39" s="3" t="n">
         <v>45881.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL36"/>
+  <dimension ref="A1:AL39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,40 +674,40 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="M2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="O2" t="n">
         <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="n">
         <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="S2" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="U2" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="V2" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -719,31 +719,31 @@
         <v>1.01</v>
       </c>
       <c r="AA2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.4</v>
+        <v>3.48</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.45</v>
+        <v>1.14</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>2.65</v>
+        <v>13.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.15</v>
+        <v>2.7</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>14</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1029,27 +1029,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,37 +1070,37 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>3.64</v>
+        <v>6.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="U5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V5" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="W5" t="n">
         <v>1.08</v>
@@ -1109,37 +1109,37 @@
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>45881.54166666666</v>
+        <v>45881.42708333334</v>
       </c>
     </row>
     <row r="6">
@@ -1161,27 +1161,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.4</v>
       </c>
-      <c r="M6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P6" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="S6" t="n">
-        <v>3.08</v>
+        <v>2.65</v>
       </c>
       <c r="T6" t="n">
-        <v>2.38</v>
+        <v>2.99</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="V6" t="n">
-        <v>5.25</v>
+        <v>7.8</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.98</v>
+        <v>3.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.45</v>
+        <v>7.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>45881.54166666666</v>
+        <v>45881.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1293,27 +1293,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,77 +1334,77 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.29</v>
+        <v>2.15</v>
       </c>
       <c r="M7" t="n">
-        <v>5.3</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>11</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="P7" t="n">
-        <v>13.75</v>
+        <v>8.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.38</v>
+        <v>3.04</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="W7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AI7" t="n">
         <v>1.09</v>
       </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>45881.54166666666</v>
+        <v>45881.52083333334</v>
       </c>
     </row>
     <row r="8">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,28 +1466,28 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
-        <v>3.88</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="P8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.56</v>
+        <v>4.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="T8" t="n">
         <v>2.38</v>
@@ -1496,46 +1496,46 @@
         <v>1.49</v>
       </c>
       <c r="V8" t="n">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="W8" t="n">
         <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z8" t="n">
         <v>1.19</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AF8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.64</v>
       </c>
-      <c r="AG8" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AH8" t="n">
-        <v>4.65</v>
+        <v>4.45</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>45881.58333333334</v>
+        <v>45881.54166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,64 +1598,64 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>3.64</v>
       </c>
       <c r="O9" t="n">
-        <v>2.25</v>
+        <v>1.64</v>
       </c>
       <c r="P9" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.93</v>
+        <v>2.63</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>2.64</v>
+        <v>2.77</v>
       </c>
       <c r="T9" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
         <v>1.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AF9" t="n">
         <v>1.85</v>
@@ -1664,10 +1664,10 @@
         <v>1.85</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45881.58333333334</v>
+        <v>45881.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,28 +1730,28 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>3.75</v>
+        <v>5.3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.65</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>13.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.66</v>
+        <v>4.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="T10" t="n">
         <v>2.38</v>
@@ -1766,37 +1766,37 @@
         <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.05</v>
+        <v>3.94</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.66</v>
+        <v>2.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AI10" t="n">
         <v>1.13</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45881.58333333334</v>
+        <v>45881.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="N11" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
         <v>1.53</v>
@@ -1901,25 +1901,25 @@
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.65</v>
+        <v>4.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AF11" t="n">
         <v>1.6</v>
@@ -1928,10 +1928,10 @@
         <v>2.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.97</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.34</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.23</v>
+        <v>1.5</v>
       </c>
       <c r="P12" t="n">
-        <v>8.1</v>
+        <v>12</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.92</v>
+        <v>2.63</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>2.67</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.93</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="V12" t="n">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.1</v>
+        <v>12</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.13</v>
+        <v>1.55</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.72</v>
+        <v>2.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.21</v>
+        <v>1.55</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>7.1</v>
+        <v>4.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P13" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC13" t="n">
         <v>1.65</v>
       </c>
-      <c r="M13" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P13" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AD13" t="n">
-        <v>2.41</v>
+        <v>3.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>1.99</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="P14" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.24</v>
+        <v>2.56</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6</v>
+        <v>3.18</v>
       </c>
       <c r="T14" t="n">
-        <v>2.84</v>
+        <v>2.38</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V14" t="n">
-        <v>7.1</v>
+        <v>5.35</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.08</v>
+        <v>3.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.99</v>
+        <v>1.64</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AH14" t="n">
-        <v>6.5</v>
+        <v>4.65</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.1</v>
+        <v>2.97</v>
       </c>
       <c r="M15" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="N15" t="n">
-        <v>1.51</v>
+        <v>2.34</v>
       </c>
       <c r="O15" t="n">
-        <v>3.02</v>
+        <v>2.23</v>
       </c>
       <c r="P15" t="n">
-        <v>16.25</v>
+        <v>8.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.38</v>
+        <v>1.92</v>
       </c>
       <c r="R15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.33</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.55</v>
-      </c>
       <c r="V15" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>8.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.58</v>
+        <v>2.13</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.23</v>
+        <v>1.71</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.88</v>
+        <v>3.72</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AF15" t="n">
         <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="M16" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.63</v>
+        <v>3.28</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>2.25</v>
+        <v>2.84</v>
       </c>
       <c r="U16" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>5</v>
+        <v>3.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.55</v>
+        <v>2.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>6.1</v>
+        <v>3.65</v>
       </c>
       <c r="O17" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="P17" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.28</v>
+        <v>2.66</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.84</v>
+        <v>2.38</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V17" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.08</v>
+        <v>4.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.71</v>
+        <v>2.09</v>
       </c>
       <c r="AH17" t="n">
-        <v>6.5</v>
+        <v>4.55</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2745,27 +2745,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P18" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.85</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P18" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG18" t="n">
-        <v>2.11</v>
+        <v>1.81</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="AL18" s="3" t="n">
-        <v>45881.60416666666</v>
+        <v>45881.58333333334</v>
       </c>
     </row>
     <row r="19">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>4.25</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>5.05</v>
+        <v>2.75</v>
       </c>
       <c r="O19" t="n">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>16.75</v>
+        <v>7.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.8</v>
+        <v>1.93</v>
       </c>
       <c r="R19" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3.34</v>
+        <v>2.64</v>
       </c>
       <c r="T19" t="n">
-        <v>2.32</v>
+        <v>2.93</v>
       </c>
       <c r="U19" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>5.45</v>
+        <v>7.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.23</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.53</v>
+        <v>3.72</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.6</v>
+        <v>7.1</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="AL19" s="3" t="n">
-        <v>45881.60416666666</v>
+        <v>45881.58333333334</v>
       </c>
     </row>
     <row r="20">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P20" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q20" t="n">
         <v>2.65</v>
       </c>
-      <c r="M20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.4</v>
+        <v>4.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.99</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.34</v>
+        <v>2.15</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="AL20" s="3" t="n">
-        <v>45881.60416666666</v>
+        <v>45881.58333333334</v>
       </c>
     </row>
     <row r="21">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="O21" t="n">
         <v>3.1</v>
@@ -3200,13 +3200,13 @@
         <v>1.53</v>
       </c>
       <c r="R21" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U21" t="n">
         <v>1.3</v>
@@ -3215,43 +3215,43 @@
         <v>6.8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
         <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.33</v>
+        <v>4.43</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH21" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>2.75</v>
       </c>
       <c r="M22" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="N22" t="n">
-        <v>9.5</v>
+        <v>2.87</v>
       </c>
       <c r="O22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="N23" t="n">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="P23" t="n">
-        <v>14.75</v>
+        <v>17</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="T23" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="U23" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="V23" t="n">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>9.1</v>
+        <v>11</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="AH23" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>45881.63541666666</v>
+        <v>45881.60416666666</v>
       </c>
     </row>
     <row r="24">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="N24" t="n">
-        <v>4.1</v>
+        <v>5.05</v>
       </c>
       <c r="O24" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P24" t="n">
-        <v>15.25</v>
+        <v>16.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="V24" t="n">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.1</v>
+        <v>11</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.92</v>
+        <v>4.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.67</v>
+        <v>2.23</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AG24" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AH24" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="AL24" s="3" t="n">
-        <v>45881.63541666666</v>
+        <v>45881.60416666666</v>
       </c>
     </row>
     <row r="25">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.68</v>
+        <v>1.29</v>
       </c>
       <c r="M25" t="n">
-        <v>3.64</v>
+        <v>4.8</v>
       </c>
       <c r="N25" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="O25" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="P25" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.02</v>
+        <v>4.75</v>
       </c>
       <c r="R25" t="n">
         <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="T25" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.99</v>
+        <v>2.55</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AH25" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="AL25" s="3" t="n">
-        <v>45881.63541666666</v>
+        <v>45881.60416666666</v>
       </c>
     </row>
     <row r="26">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="O26" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="P26" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.46</v>
+        <v>3.02</v>
       </c>
       <c r="R26" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="U26" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.89</v>
+        <v>2.09</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.48</v>
+        <v>3.62</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AH26" t="n">
-        <v>6.85</v>
+        <v>7.3</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="P27" t="n">
-        <v>13</v>
+        <v>15.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="R27" t="n">
         <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="V27" t="n">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="W27" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>13</v>
+        <v>9.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.6</v>
+        <v>3.92</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.35</v>
+        <v>2.67</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="AL27" s="3" t="n">
-        <v>45881.66666666666</v>
+        <v>45881.63541666666</v>
       </c>
     </row>
     <row r="28">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="AL28" s="3" t="n">
-        <v>45881.66666666666</v>
+        <v>45881.63541666666</v>
       </c>
     </row>
     <row r="29">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="O29" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="P29" t="n">
-        <v>11.5</v>
+        <v>14.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
         <v>3.2</v>
       </c>
       <c r="T29" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V29" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="W29" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>13</v>
+        <v>9.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC29" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AH29" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="AL29" s="3" t="n">
-        <v>45881.66666666666</v>
+        <v>45881.63541666666</v>
       </c>
     </row>
     <row r="30">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4461,27 +4461,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="M31" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="P31" t="n">
-        <v>19.75</v>
+        <v>11.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="U31" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="V31" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W31" t="n">
         <v>1.12</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AA31" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.84</v>
+        <v>4.65</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="AL31" s="3" t="n">
-        <v>45881.79166666666</v>
+        <v>45881.66666666666</v>
       </c>
     </row>
     <row r="32">
@@ -4593,27 +4593,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="M32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q32" t="n">
         <v>3</v>
       </c>
-      <c r="N32" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P32" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD32" t="n">
         <v>2.6</v>
       </c>
-      <c r="R32" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AE32" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AH32" t="n">
-        <v>9.25</v>
+        <v>4.65</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="AL32" s="3" t="n">
-        <v>45881.79166666666</v>
+        <v>45881.66666666666</v>
       </c>
     </row>
     <row r="33">
@@ -4725,27 +4725,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="M33" t="n">
-        <v>3.06</v>
+        <v>3.9</v>
       </c>
       <c r="N33" t="n">
-        <v>3.64</v>
+        <v>4.7</v>
       </c>
       <c r="O33" t="n">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="P33" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="R33" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="S33" t="n">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="T33" t="n">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="U33" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="V33" t="n">
-        <v>8.5</v>
+        <v>5.25</v>
       </c>
       <c r="W33" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X33" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="AD33" t="n">
-        <v>4.5</v>
+        <v>2.35</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="AF33" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="n">
-        <v>10</v>
+        <v>4.3</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="AL33" s="3" t="n">
-        <v>45881.8125</v>
+        <v>45881.66666666666</v>
       </c>
     </row>
     <row r="34">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N34" t="n">
+        <v>6</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P34" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V34" t="n">
+        <v>5</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG34" t="n">
         <v>2.03</v>
       </c>
-      <c r="M34" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V34" t="n">
-        <v>11</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="AL34" s="3" t="n">
-        <v>45881.89583333334</v>
+        <v>45881.79166666666</v>
       </c>
     </row>
     <row r="35">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.56</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>2.67</v>
+        <v>3.65</v>
       </c>
       <c r="O35" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="R35" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S35" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="T35" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V35" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="W35" t="n">
         <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="AL35" s="3" t="n">
-        <v>45881.89583333334</v>
+        <v>45881.79166666666</v>
       </c>
     </row>
     <row r="36">
@@ -5121,129 +5121,525 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P36" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V36" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL36" s="3" t="n">
+        <v>45881.8125</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V37" t="n">
+        <v>11</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL37" s="3" t="n">
+        <v>45881.89583333334</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>Bolivia LFPB</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Wilstermann</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="inlineStr">
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="L38" t="n">
         <v>2.25</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M38" t="n">
         <v>3.75</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N38" t="n">
         <v>2.7</v>
       </c>
-      <c r="O36" t="n">
+      <c r="O38" t="n">
         <v>1.95</v>
       </c>
-      <c r="P36" t="n">
+      <c r="P38" t="n">
         <v>11.5</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="Q38" t="n">
         <v>1.91</v>
       </c>
-      <c r="R36" t="n">
+      <c r="R38" t="n">
         <v>1.36</v>
       </c>
-      <c r="S36" t="n">
+      <c r="S38" t="n">
         <v>3</v>
       </c>
-      <c r="T36" t="n">
+      <c r="T38" t="n">
         <v>2.63</v>
       </c>
-      <c r="U36" t="n">
+      <c r="U38" t="n">
         <v>1.44</v>
       </c>
-      <c r="V36" t="n">
+      <c r="V38" t="n">
         <v>7</v>
       </c>
-      <c r="W36" t="n">
+      <c r="W38" t="n">
         <v>1.1</v>
       </c>
-      <c r="X36" t="n">
+      <c r="X38" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="Y38" t="n">
         <v>13</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="Z38" t="n">
         <v>1.22</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AA38" t="n">
         <v>3.9</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AB38" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AC38" t="n">
         <v>2.18</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AD38" t="n">
         <v>2.75</v>
       </c>
-      <c r="AE36" t="n">
+      <c r="AE38" t="n">
         <v>1.42</v>
       </c>
-      <c r="AF36" t="n">
+      <c r="AF38" t="n">
         <v>1.67</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AG38" t="n">
         <v>2.1</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AH38" t="n">
         <v>5.5</v>
       </c>
-      <c r="AI36" t="n">
+      <c r="AI38" t="n">
         <v>1.14</v>
       </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL36" s="3" t="n">
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL38" s="3" t="n">
+        <v>45881.89583333334</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V39" t="n">
+        <v>11</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL39" s="3" t="n">
         <v>45881.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="M2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O2" t="n">
         <v>1.13</v>
@@ -722,10 +722,10 @@
         <v>11.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.3</v>
+        <v>4.91</v>
       </c>
       <c r="AD2" t="n">
         <v>1.37</v>
@@ -740,10 +740,10 @@
         <v>1.67</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.14</v>
+        <v>2.45</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>13.5</v>
+        <v>2.65</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="P3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.7</v>
+        <v>1.15</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="N4" t="n">
-        <v>2.25</v>
+        <v>14</v>
       </c>
       <c r="O4" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>2.94</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="N5" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="O5" t="n">
         <v>1.44</v>
@@ -1118,10 +1118,10 @@
         <v>3.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AD5" t="n">
         <v>2.9</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="O6" t="n">
         <v>2.4</v>
@@ -1250,10 +1250,10 @@
         <v>3.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AD6" t="n">
         <v>3.3</v>
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
         <v>1.8</v>
@@ -1382,10 +1382,10 @@
         <v>3.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD7" t="n">
         <v>3.5</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.65</v>
+        <v>2.97</v>
       </c>
       <c r="M11" t="n">
-        <v>4.15</v>
+        <v>3.44</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>2.34</v>
       </c>
       <c r="O11" t="n">
-        <v>1.53</v>
+        <v>2.23</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>8.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.65</v>
+        <v>1.92</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>2.67</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="U11" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>5.25</v>
+        <v>7.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>13</v>
+        <v>8.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.45</v>
+        <v>2.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.62</v>
+        <v>2.13</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.3</v>
+        <v>1.71</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.41</v>
+        <v>3.72</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.88</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.56</v>
+        <v>1.93</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>3.18</v>
+        <v>2.64</v>
       </c>
       <c r="T14" t="n">
-        <v>2.38</v>
+        <v>2.93</v>
       </c>
       <c r="U14" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>5.35</v>
+        <v>7.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.95</v>
+        <v>2.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.62</v>
+        <v>3.72</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.65</v>
+        <v>7.1</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,34 +2390,34 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.97</v>
+        <v>1.61</v>
       </c>
       <c r="M15" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>2.34</v>
+        <v>6.1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.23</v>
+        <v>1.51</v>
       </c>
       <c r="P15" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.92</v>
+        <v>3.28</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
         <v>7.1</v>
@@ -2429,37 +2429,37 @@
         <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="AC15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.71</v>
       </c>
-      <c r="AD15" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH15" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>6.1</v>
+        <v>3.65</v>
       </c>
       <c r="O16" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="P16" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.28</v>
+        <v>2.66</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.84</v>
+        <v>2.38</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V16" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.08</v>
+        <v>4.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.71</v>
+        <v>2.09</v>
       </c>
       <c r="AH16" t="n">
-        <v>6.5</v>
+        <v>4.55</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="N17" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.05</v>
+        <v>4.45</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2804,58 +2804,58 @@
         <v>1.38</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="U18" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AE18" t="n">
         <v>1.37</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AH18" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.88</v>
       </c>
       <c r="N19" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="P19" t="n">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.93</v>
+        <v>2.56</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>2.64</v>
+        <v>3.18</v>
       </c>
       <c r="T19" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="V19" t="n">
-        <v>7.2</v>
+        <v>5.35</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.88</v>
+        <v>3.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.72</v>
+        <v>2.62</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>7.1</v>
+        <v>4.65</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5.8</v>
+        <v>2.65</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="N21" t="n">
-        <v>1.66</v>
+        <v>2.9</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.33</v>
+        <v>2.99</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.75</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.87</v>
+        <v>9.5</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.4</v>
+        <v>3.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3446,28 +3446,28 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="M23" t="n">
-        <v>3.85</v>
+        <v>4.25</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>5.05</v>
       </c>
       <c r="O23" t="n">
         <v>1.48</v>
       </c>
       <c r="P23" t="n">
-        <v>17</v>
+        <v>16.75</v>
       </c>
       <c r="Q23" t="n">
         <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S23" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="T23" t="n">
         <v>2.32</v>
@@ -3476,10 +3476,10 @@
         <v>1.51</v>
       </c>
       <c r="V23" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
@@ -3488,31 +3488,31 @@
         <v>11</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AH23" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AI23" t="n">
         <v>1.13</v>
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>4.25</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
         <v>1.48</v>
       </c>
       <c r="P24" t="n">
-        <v>16.75</v>
+        <v>17</v>
       </c>
       <c r="Q24" t="n">
         <v>2.8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="T24" t="n">
         <v>2.32</v>
@@ -3608,10 +3608,10 @@
         <v>1.51</v>
       </c>
       <c r="V24" t="n">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
@@ -3620,31 +3620,31 @@
         <v>11</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AB24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF24" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC24" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AG24" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AH24" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AI24" t="n">
         <v>1.13</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.29</v>
+        <v>5.9</v>
       </c>
       <c r="M25" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>9</v>
+        <v>1.55</v>
       </c>
       <c r="O25" t="n">
-        <v>1.26</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.75</v>
+        <v>1.53</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S25" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="T25" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AI25" t="n">
         <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.12</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="M26" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>5.4</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.02</v>
+        <v>3.46</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="T26" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V26" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.02</v>
+        <v>3.16</v>
       </c>
       <c r="AB26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF26" t="n">
         <v>2.09</v>
       </c>
-      <c r="AC26" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AH26" t="n">
-        <v>7.3</v>
+        <v>6.85</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N28" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P28" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA28" t="n">
         <v>3.85</v>
       </c>
-      <c r="O28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P28" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V28" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.16</v>
-      </c>
       <c r="AB28" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.48</v>
+        <v>2.7</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.09</v>
+        <v>1.7</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="AH28" t="n">
-        <v>6.85</v>
+        <v>4.8</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>3.64</v>
       </c>
       <c r="N29" t="n">
-        <v>4.55</v>
+        <v>5.4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P29" t="n">
-        <v>14.75</v>
+        <v>8.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T29" t="n">
-        <v>2.42</v>
+        <v>2.93</v>
       </c>
       <c r="U29" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>5.45</v>
+        <v>7.8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.85</v>
+        <v>3.02</v>
       </c>
       <c r="AB29" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC29" t="n">
         <v>1.74</v>
       </c>
-      <c r="AC29" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AD29" t="n">
-        <v>2.7</v>
+        <v>3.62</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.03</v>
+        <v>1.73</v>
       </c>
       <c r="AH29" t="n">
-        <v>4.8</v>
+        <v>7.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="O31" t="n">
         <v>1.44</v>
@@ -4538,10 +4538,10 @@
         <v>1.12</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z31" t="n">
         <v>1.18</v>
@@ -4550,10 +4550,10 @@
         <v>4.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AD31" t="n">
         <v>2.6</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M33" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P33" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S33" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U33" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
         <v>13</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH33" t="n">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="O34" t="n">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="P34" t="n">
-        <v>19.75</v>
+        <v>6.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.24</v>
+        <v>2.6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="S34" t="n">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="T34" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="U34" t="n">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="V34" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>17</v>
+        <v>6.25</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="AA34" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.46</v>
+        <v>2.55</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.84</v>
+        <v>9.25</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="N35" t="n">
+        <v>6</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P35" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S35" t="n">
         <v>3.65</v>
       </c>
-      <c r="O35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P35" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.35</v>
-      </c>
       <c r="T35" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="U35" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="V35" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z35" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y35" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA35" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.55</v>
+        <v>1.46</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AI35" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.05</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>2.4</v>
       </c>
       <c r="R36" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="S36" t="n">
         <v>2.45</v>
@@ -5192,7 +5192,7 @@
         <v>1.29</v>
       </c>
       <c r="V36" t="n">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="W36" t="n">
         <v>1.05</v>
@@ -5201,7 +5201,7 @@
         <v>1.07</v>
       </c>
       <c r="Y36" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="Z36" t="n">
         <v>1.42</v>
@@ -5216,10 +5216,10 @@
         <v>1.53</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AF36" t="n">
         <v>2</v>
@@ -5231,7 +5231,7 @@
         <v>10</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,22 +5294,22 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.03</v>
+        <v>2.56</v>
       </c>
       <c r="M37" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="N37" t="n">
-        <v>3.52</v>
+        <v>2.67</v>
       </c>
       <c r="O37" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="R37" t="n">
         <v>1.53</v>
@@ -5318,10 +5318,10 @@
         <v>2.38</v>
       </c>
       <c r="T37" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U37" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V37" t="n">
         <v>11</v>
@@ -5336,16 +5336,16 @@
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5354,10 +5354,10 @@
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="M38" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T38" t="n">
         <v>3.75</v>
       </c>
-      <c r="N38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P38" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U38" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V38" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W38" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="AB38" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG38" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC38" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH38" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="M39" t="n">
-        <v>2.83</v>
+        <v>3.75</v>
       </c>
       <c r="N39" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="O39" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="R39" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S39" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="U39" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="V39" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.25</v>
+        <v>3.9</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.48</v>
+        <v>1.62</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.45</v>
+        <v>1.15</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>2.65</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="AC3" t="n">
-        <v>2</v>
+        <v>2.94</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.15</v>
+        <v>2.45</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>14</v>
+        <v>2.65</v>
       </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="P4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.94</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1466,19 +1466,19 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="N8" t="n">
-        <v>8.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="O8" t="n">
         <v>1.27</v>
       </c>
       <c r="P8" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="Q8" t="n">
         <v>4.3</v>
@@ -1496,7 +1496,7 @@
         <v>1.49</v>
       </c>
       <c r="V8" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="W8" t="n">
         <v>1.09</v>
@@ -1511,13 +1511,13 @@
         <v>1.19</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
         <v>2.56</v>
@@ -1526,16 +1526,16 @@
         <v>1.42</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.38</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>3.64</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P9" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.64</v>
       </c>
-      <c r="P9" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V9" t="n">
-        <v>7</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH9" t="n">
-        <v>6.6</v>
+        <v>4.45</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>1.89</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>3.38</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>3.64</v>
       </c>
       <c r="O10" t="n">
-        <v>1.27</v>
+        <v>1.64</v>
       </c>
       <c r="P10" t="n">
-        <v>13.75</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.3</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="T10" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.97</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>2.34</v>
+        <v>3.65</v>
       </c>
       <c r="O11" t="n">
-        <v>2.23</v>
+        <v>1.54</v>
       </c>
       <c r="P11" t="n">
-        <v>8.1</v>
+        <v>15</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.92</v>
+        <v>2.66</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="V11" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.9</v>
+        <v>4.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.13</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.72</v>
+        <v>2.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="AH11" t="n">
-        <v>7.1</v>
+        <v>4.55</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>5.1</v>
       </c>
       <c r="M12" t="n">
         <v>4.1</v>
       </c>
       <c r="N12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P12" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>7</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH12" t="n">
         <v>5</v>
       </c>
-      <c r="O12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P12" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AI12" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="M13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S13" t="n">
         <v>3.3</v>
       </c>
-      <c r="N13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P13" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.6</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>5.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.08</v>
+        <v>4.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.99</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="n">
-        <v>6.5</v>
+        <v>4.05</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2390,22 +2390,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P15" t="n">
         <v>8</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="R15" t="n">
         <v>1.41</v>
@@ -2438,10 +2438,10 @@
         <v>3.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AD15" t="n">
         <v>3.4</v>
@@ -2450,10 +2450,10 @@
         <v>1.25</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AH15" t="n">
         <v>6.5</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="P16" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="V16" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z16" t="n">
         <v>1.18</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="M17" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>4.8</v>
+        <v>6.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.65</v>
+        <v>3.28</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.84</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>5.25</v>
+        <v>7.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.45</v>
+        <v>3.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.62</v>
+        <v>2.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.41</v>
+        <v>3.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.15</v>
+        <v>1.71</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.1</v>
+        <v>2.97</v>
       </c>
       <c r="M18" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="N18" t="n">
-        <v>1.51</v>
+        <v>2.34</v>
       </c>
       <c r="O18" t="n">
-        <v>3.02</v>
+        <v>2.23</v>
       </c>
       <c r="P18" t="n">
-        <v>16.25</v>
+        <v>8.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.38</v>
+        <v>1.92</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA18" t="n">
         <v>2.9</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.92</v>
+        <v>3.72</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.88</v>
+        <v>4.15</v>
       </c>
       <c r="N19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH19" t="n">
         <v>4.2</v>
       </c>
-      <c r="O19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>4.65</v>
-      </c>
       <c r="AI19" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="N20" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="P20" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="T20" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="U20" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="V20" t="n">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AA20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH20" t="n">
         <v>4.65</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>4.05</v>
-      </c>
       <c r="AI20" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.65</v>
+        <v>1.61</v>
       </c>
       <c r="M21" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P21" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2.8</v>
       </c>
-      <c r="N21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.99</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.34</v>
+        <v>2.23</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>2.65</v>
       </c>
       <c r="M22" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="N22" t="n">
-        <v>9.5</v>
+        <v>2.9</v>
       </c>
       <c r="O22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.04</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>2.99</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.61</v>
+        <v>5.9</v>
       </c>
       <c r="M23" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="N23" t="n">
-        <v>5.05</v>
+        <v>1.55</v>
       </c>
       <c r="O23" t="n">
-        <v>1.48</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>16.75</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.8</v>
+        <v>1.53</v>
       </c>
       <c r="R23" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="S23" t="n">
-        <v>3.34</v>
+        <v>2.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.32</v>
+        <v>3.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>5.45</v>
+        <v>6.8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AI23" t="n">
         <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.13</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="P24" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>3.42</v>
+        <v>2.86</v>
       </c>
       <c r="T24" t="n">
-        <v>2.32</v>
+        <v>2.84</v>
       </c>
       <c r="U24" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.45</v>
+        <v>3.04</v>
       </c>
       <c r="AB24" t="n">
         <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.11</v>
+        <v>1.45</v>
       </c>
       <c r="AH24" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.9</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>1.55</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>1.48</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.53</v>
+        <v>2.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6</v>
+        <v>3.42</v>
       </c>
       <c r="T25" t="n">
-        <v>3.2</v>
+        <v>2.32</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="V25" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.56</v>
+        <v>4.45</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC25" t="n">
         <v>2</v>
       </c>
-      <c r="AC25" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AD25" t="n">
-        <v>4.43</v>
+        <v>2.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.6</v>
+        <v>2.11</v>
       </c>
       <c r="AH25" t="n">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="M26" t="n">
         <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="P26" t="n">
-        <v>9</v>
+        <v>15.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.46</v>
+        <v>2.81</v>
       </c>
       <c r="R26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AE26" t="n">
         <v>1.39</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V26" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AF26" t="n">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>6.85</v>
+        <v>4.7</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="M27" t="n">
         <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O27" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="P27" t="n">
-        <v>15.25</v>
+        <v>9</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.81</v>
+        <v>3.46</v>
       </c>
       <c r="R27" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V27" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z27" t="n">
         <v>1.28</v>
       </c>
-      <c r="S27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V27" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AA27" t="n">
-        <v>3.92</v>
+        <v>3.16</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.67</v>
+        <v>3.48</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.72</v>
+        <v>2.09</v>
       </c>
       <c r="AG27" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.7</v>
+        <v>6.85</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M30" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P30" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S30" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T30" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U30" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V30" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
         <v>13</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O33" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P33" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R33" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S33" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T33" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="U33" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V33" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="W33" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
         <v>13</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="n">
-        <v>4.65</v>
+        <v>4.3</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="M37" t="n">
-        <v>2.83</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="O37" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="R37" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S37" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="U37" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="V37" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.25</v>
+        <v>3.9</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.48</v>
+        <v>1.62</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V39" t="n">
+        <v>11</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA39" t="n">
         <v>2.25</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P39" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V39" t="n">
-        <v>7</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AB39" t="n">
-        <v>1.62</v>
+        <v>2.48</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.18</v>
+        <v>1.47</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AH39" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.15</v>
+        <v>2.45</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>14</v>
+        <v>2.65</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="P3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.94</v>
+        <v>2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.45</v>
+        <v>1.15</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="N4" t="n">
-        <v>2.65</v>
+        <v>14</v>
       </c>
       <c r="O4" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>2.94</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M5" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="N5" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="O5" t="n">
         <v>1.44</v>
@@ -1088,58 +1088,58 @@
         <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="T5" t="n">
         <v>2.72</v>
       </c>
       <c r="U5" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="Z5" t="n">
         <v>1.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AH5" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
         <v>3.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="O6" t="n">
         <v>2.4</v>
@@ -1220,19 +1220,19 @@
         <v>1.73</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="T6" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="U6" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="V6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="W6" t="n">
         <v>1.05</v>
@@ -1241,25 +1241,25 @@
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AD6" t="n">
         <v>3.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AF6" t="n">
         <v>1.77</v>
@@ -1268,10 +1268,10 @@
         <v>1.87</v>
       </c>
       <c r="AH6" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O7" t="n">
         <v>1.8</v>
@@ -1355,13 +1355,13 @@
         <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T7" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
         <v>7.8</v>
@@ -1376,34 +1376,34 @@
         <v>8.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6</v>
+        <v>3.38</v>
       </c>
       <c r="N9" t="n">
-        <v>8.300000000000001</v>
+        <v>3.64</v>
       </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>1.64</v>
       </c>
       <c r="P9" t="n">
-        <v>14</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.3</v>
+        <v>2.63</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="T9" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.98</v>
+        <v>3.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.45</v>
+        <v>6.6</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.38</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>3.64</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P10" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.64</v>
       </c>
-      <c r="P10" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH10" t="n">
-        <v>6.6</v>
+        <v>4.45</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="P11" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.66</v>
+        <v>3.24</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.38</v>
+        <v>2.84</v>
       </c>
       <c r="U11" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.05</v>
+        <v>3.08</v>
       </c>
       <c r="AB11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC11" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC11" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD11" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.66</v>
+        <v>1.99</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.55</v>
+        <v>6.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.1</v>
+        <v>2.97</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="N12" t="n">
-        <v>1.51</v>
+        <v>2.34</v>
       </c>
       <c r="O12" t="n">
-        <v>3.02</v>
+        <v>2.23</v>
       </c>
       <c r="P12" t="n">
-        <v>16.25</v>
+        <v>8.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.38</v>
+        <v>1.92</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V12" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2.9</v>
       </c>
-      <c r="T12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V12" t="n">
-        <v>7</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.92</v>
+        <v>3.72</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AH12" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="O14" t="n">
-        <v>2.25</v>
+        <v>1.54</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.93</v>
+        <v>2.66</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="V14" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.88</v>
+        <v>4.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.72</v>
+        <v>2.6</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="AH14" t="n">
-        <v>7.1</v>
+        <v>4.55</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="P15" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.24</v>
+        <v>2.56</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>3.18</v>
       </c>
       <c r="T15" t="n">
-        <v>2.84</v>
+        <v>2.38</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V15" t="n">
-        <v>7.1</v>
+        <v>5.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
         <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.08</v>
+        <v>3.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.99</v>
+        <v>1.64</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>6.5</v>
+        <v>4.65</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="M16" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="P16" t="n">
         <v>12</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="R16" t="n">
         <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T16" t="n">
         <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V16" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="W16" t="n">
         <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AA16" t="n">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
         <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2786,28 +2786,28 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.97</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="T18" t="n">
         <v>2.93</v>
@@ -2816,28 +2816,28 @@
         <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
         <v>3.72</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="M19" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="P19" t="n">
         <v>12</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="R19" t="n">
         <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T19" t="n">
         <v>2.25</v>
       </c>
       <c r="U19" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="V19" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W19" t="n">
         <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
         <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P20" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>7</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.79</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AH20" t="n">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3182,28 +3182,28 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>4.25</v>
+        <v>3.85</v>
       </c>
       <c r="N21" t="n">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>1.48</v>
       </c>
       <c r="P21" t="n">
-        <v>16.75</v>
+        <v>17</v>
       </c>
       <c r="Q21" t="n">
         <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="T21" t="n">
         <v>2.32</v>
@@ -3212,10 +3212,10 @@
         <v>1.51</v>
       </c>
       <c r="V21" t="n">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
@@ -3224,31 +3224,31 @@
         <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF21" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC21" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AG21" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AH21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AI21" t="n">
         <v>1.13</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.65</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.9</v>
+        <v>9.5</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.4</v>
+        <v>3.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.99</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.34</v>
+        <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5.9</v>
+        <v>2.65</v>
       </c>
       <c r="M23" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="N23" t="n">
-        <v>1.55</v>
+        <v>2.9</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>2</v>
+        <v>2.99</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.3</v>
       </c>
-      <c r="M24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N24" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P24" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AI24" t="n">
         <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.12</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3710,28 +3710,28 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>4.25</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>5.05</v>
       </c>
       <c r="O25" t="n">
         <v>1.48</v>
       </c>
       <c r="P25" t="n">
-        <v>17</v>
+        <v>16.75</v>
       </c>
       <c r="Q25" t="n">
         <v>2.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S25" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="T25" t="n">
         <v>2.32</v>
@@ -3740,10 +3740,10 @@
         <v>1.51</v>
       </c>
       <c r="V25" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
@@ -3752,31 +3752,31 @@
         <v>11</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AI25" t="n">
         <v>1.13</v>
@@ -3842,22 +3842,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>4.55</v>
       </c>
       <c r="O26" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="P26" t="n">
-        <v>15.25</v>
+        <v>14.75</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="R26" t="n">
         <v>1.28</v>
@@ -3866,16 +3866,16 @@
         <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U26" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V26" t="n">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="W26" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
         <v>1</v>
@@ -3884,34 +3884,34 @@
         <v>9.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.2</v>
+        <v>1.74</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.67</v>
+        <v>2.09</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AH26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1</v>
+        <v>3.64</v>
       </c>
       <c r="N28" t="n">
-        <v>4.55</v>
+        <v>5.4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P28" t="n">
-        <v>14.75</v>
+        <v>8.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.42</v>
+        <v>2.93</v>
       </c>
       <c r="U28" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
-        <v>5.45</v>
+        <v>7.8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.85</v>
+        <v>3.02</v>
       </c>
       <c r="AB28" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC28" t="n">
         <v>1.74</v>
       </c>
-      <c r="AC28" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AD28" t="n">
-        <v>2.7</v>
+        <v>3.62</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.03</v>
+        <v>1.73</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.8</v>
+        <v>7.3</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="M29" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="P29" t="n">
-        <v>8.6</v>
+        <v>15.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="R29" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="T29" t="n">
-        <v>2.93</v>
+        <v>2.4</v>
       </c>
       <c r="U29" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>7.8</v>
+        <v>5.35</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.02</v>
+        <v>3.92</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.62</v>
+        <v>2.67</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="n">
-        <v>7.3</v>
+        <v>4.7</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O30" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P30" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R30" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="U30" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V30" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
         <v>13</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.65</v>
+        <v>4.3</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="M33" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="N33" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="O33" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P33" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S33" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U33" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X33" t="n">
         <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH33" t="n">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="N34" t="n">
+        <v>6</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P34" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S34" t="n">
         <v>3.65</v>
       </c>
-      <c r="O34" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P34" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.35</v>
-      </c>
       <c r="T34" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="U34" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="V34" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z34" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y34" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA34" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.55</v>
+        <v>1.46</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AI34" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.05</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="O35" t="n">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="P35" t="n">
-        <v>19.75</v>
+        <v>6.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.24</v>
+        <v>2.6</v>
       </c>
       <c r="R35" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="S35" t="n">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="T35" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="V35" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>17</v>
+        <v>6.25</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="AA35" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.46</v>
+        <v>2.55</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AH35" t="n">
-        <v>3.84</v>
+        <v>9.25</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,22 +5426,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.03</v>
+        <v>2.56</v>
       </c>
       <c r="M38" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="N38" t="n">
-        <v>3.52</v>
+        <v>2.67</v>
       </c>
       <c r="O38" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="R38" t="n">
         <v>1.53</v>
@@ -5450,10 +5450,10 @@
         <v>2.38</v>
       </c>
       <c r="T38" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U38" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V38" t="n">
         <v>11</v>
@@ -5468,16 +5468,16 @@
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5486,10 +5486,10 @@
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,22 +5558,22 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.56</v>
+        <v>2.03</v>
       </c>
       <c r="M39" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="N39" t="n">
-        <v>2.67</v>
+        <v>3.52</v>
       </c>
       <c r="O39" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="R39" t="n">
         <v>1.53</v>
@@ -5582,10 +5582,10 @@
         <v>2.38</v>
       </c>
       <c r="T39" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U39" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V39" t="n">
         <v>11</v>
@@ -5600,16 +5600,16 @@
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5618,10 +5618,10 @@
         <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH39" t="n">
         <v>0</v>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.45</v>
+        <v>1.15</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>2.65</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="AC3" t="n">
-        <v>2</v>
+        <v>2.94</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.15</v>
+        <v>2.45</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>14</v>
+        <v>2.65</v>
       </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="P4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.94</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.24</v>
+        <v>2.63</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.08</v>
+        <v>5</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>6.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.97</v>
+        <v>5.1</v>
       </c>
       <c r="M12" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.34</v>
+        <v>1.51</v>
       </c>
       <c r="O12" t="n">
-        <v>2.23</v>
+        <v>3.02</v>
       </c>
       <c r="P12" t="n">
-        <v>8.1</v>
+        <v>16.25</v>
       </c>
       <c r="Q12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>7</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.92</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V12" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AH12" t="n">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N13" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.25</v>
       </c>
-      <c r="U13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AD13" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.95</v>
+        <v>2.97</v>
       </c>
       <c r="M14" t="n">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="N14" t="n">
-        <v>3.65</v>
+        <v>2.34</v>
       </c>
       <c r="O14" t="n">
-        <v>1.54</v>
+        <v>2.23</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>8.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.66</v>
+        <v>1.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="T14" t="n">
-        <v>2.38</v>
+        <v>2.93</v>
       </c>
       <c r="U14" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.05</v>
+        <v>2.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.6</v>
+        <v>3.72</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.55</v>
+        <v>7.1</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.88</v>
+        <v>4.15</v>
       </c>
       <c r="N15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P15" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH15" t="n">
         <v>4.2</v>
       </c>
-      <c r="O15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>4.65</v>
-      </c>
       <c r="AI15" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="M16" t="n">
-        <v>4.15</v>
+        <v>3.88</v>
       </c>
       <c r="N16" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="P16" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="T16" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="U16" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="V16" t="n">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.45</v>
+        <v>3.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="M17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N17" t="n">
         <v>3.7</v>
       </c>
-      <c r="N17" t="n">
-        <v>6.1</v>
-      </c>
       <c r="O17" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.28</v>
+        <v>2.65</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>7.1</v>
+        <v>5.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.08</v>
+        <v>4.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>6.5</v>
+        <v>4.05</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="M19" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.63</v>
+        <v>3.28</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>2.84</v>
       </c>
       <c r="U19" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="V19" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>5</v>
+        <v>3.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.55</v>
+        <v>2.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="M20" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>1.51</v>
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
-        <v>3.02</v>
+        <v>1.52</v>
       </c>
       <c r="P20" t="n">
-        <v>16.25</v>
+        <v>8</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.38</v>
+        <v>3.24</v>
       </c>
       <c r="R20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.35</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.9</v>
+        <v>3.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AH20" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3182,28 +3182,28 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="M21" t="n">
-        <v>3.85</v>
+        <v>4.25</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>5.05</v>
       </c>
       <c r="O21" t="n">
         <v>1.48</v>
       </c>
       <c r="P21" t="n">
-        <v>17</v>
+        <v>16.75</v>
       </c>
       <c r="Q21" t="n">
         <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="T21" t="n">
         <v>2.32</v>
@@ -3212,10 +3212,10 @@
         <v>1.51</v>
       </c>
       <c r="V21" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
@@ -3224,31 +3224,31 @@
         <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AH21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AI21" t="n">
         <v>1.13</v>
@@ -3710,28 +3710,28 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>4.25</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
         <v>1.48</v>
       </c>
       <c r="P25" t="n">
-        <v>16.75</v>
+        <v>17</v>
       </c>
       <c r="Q25" t="n">
         <v>2.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="T25" t="n">
         <v>2.32</v>
@@ -3740,10 +3740,10 @@
         <v>1.51</v>
       </c>
       <c r="V25" t="n">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
@@ -3752,31 +3752,31 @@
         <v>11</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AG25" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AI25" t="n">
         <v>1.13</v>
@@ -3842,22 +3842,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="M26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N26" t="n">
         <v>4.1</v>
       </c>
-      <c r="N26" t="n">
-        <v>4.55</v>
-      </c>
       <c r="O26" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="P26" t="n">
-        <v>14.75</v>
+        <v>15.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="R26" t="n">
         <v>1.28</v>
@@ -3866,16 +3866,16 @@
         <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U26" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V26" t="n">
-        <v>5.45</v>
+        <v>5.35</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
         <v>1</v>
@@ -3884,34 +3884,34 @@
         <v>9.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.09</v>
+        <v>1.67</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N27" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P27" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V27" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA27" t="n">
         <v>3.85</v>
       </c>
-      <c r="O27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P27" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V27" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.16</v>
-      </c>
       <c r="AB27" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.48</v>
+        <v>2.7</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.09</v>
+        <v>1.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="AH27" t="n">
-        <v>6.85</v>
+        <v>4.8</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="M28" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>5.4</v>
+        <v>3.85</v>
       </c>
       <c r="O28" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="P28" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.02</v>
+        <v>3.46</v>
       </c>
       <c r="R28" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="T28" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="U28" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.02</v>
+        <v>3.16</v>
       </c>
       <c r="AB28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF28" t="n">
         <v>2.09</v>
       </c>
-      <c r="AC28" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AG28" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AH28" t="n">
-        <v>7.3</v>
+        <v>6.85</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="N29" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="P29" t="n">
-        <v>15.25</v>
+        <v>8.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T29" t="n">
-        <v>2.4</v>
+        <v>2.93</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>5.35</v>
+        <v>7.8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.92</v>
+        <v>3.02</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.67</v>
+        <v>3.62</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="AG29" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AH29" t="n">
-        <v>4.7</v>
+        <v>7.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="O34" t="n">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="P34" t="n">
-        <v>19.75</v>
+        <v>6.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.24</v>
+        <v>2.6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="S34" t="n">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="T34" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="U34" t="n">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="V34" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>17</v>
+        <v>6.25</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="AA34" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.46</v>
+        <v>2.55</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.84</v>
+        <v>9.25</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="N35" t="n">
+        <v>6</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P35" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S35" t="n">
         <v>3.65</v>
       </c>
-      <c r="O35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P35" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.35</v>
-      </c>
       <c r="T35" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="U35" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="V35" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z35" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y35" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA35" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.55</v>
+        <v>1.46</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AI35" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.05</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P37" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V37" t="n">
+        <v>11</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA37" t="n">
         <v>2.25</v>
       </c>
-      <c r="M37" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P37" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V37" t="n">
-        <v>7</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AB37" t="n">
-        <v>1.62</v>
+        <v>2.48</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.18</v>
+        <v>1.47</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.75</v>
+        <v>4.75</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AH37" t="n">
-        <v>5.5</v>
+        <v>9.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="M38" t="n">
-        <v>2.83</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="O38" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="R38" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="U38" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="V38" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W38" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.25</v>
+        <v>3.9</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.48</v>
+        <v>1.62</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>1.8</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q39" t="n">
         <v>2.4</v>
@@ -5594,10 +5594,10 @@
         <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z39" t="n">
         <v>1.55</v>
@@ -5612,10 +5612,10 @@
         <v>1.49</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF39" t="n">
         <v>2.2</v>
@@ -5624,10 +5624,10 @@
         <v>1.62</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="M2" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="N2" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="O2" t="n">
         <v>1.13</v>
@@ -698,16 +698,16 @@
         <v>5.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="U2" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="V2" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -722,28 +722,28 @@
         <v>11.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.91</v>
+        <v>5.35</v>
       </c>
       <c r="AD2" t="n">
         <v>1.37</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.48</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI2" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.75</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.15</v>
+        <v>1.93</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>3.78</v>
       </c>
       <c r="N3" t="n">
-        <v>14</v>
+        <v>2.96</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="P3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.45</v>
+        <v>1.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>7.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.65</v>
+        <v>12.5</v>
       </c>
       <c r="O4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P4" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1.91</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
         <v>3.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="O6" t="n">
         <v>2.4</v>
@@ -1250,10 +1250,10 @@
         <v>2.97</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AD6" t="n">
         <v>3.3</v>
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
         <v>1.8</v>
@@ -1382,10 +1382,10 @@
         <v>2.97</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AD7" t="n">
         <v>3.58</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.29</v>
+        <v>1.89</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3</v>
+        <v>3.38</v>
       </c>
       <c r="N8" t="n">
-        <v>11</v>
+        <v>3.64</v>
       </c>
       <c r="O8" t="n">
-        <v>1.27</v>
+        <v>1.64</v>
       </c>
       <c r="P8" t="n">
-        <v>13.75</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.3</v>
+        <v>2.63</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="T8" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.38</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>3.64</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P9" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.64</v>
       </c>
-      <c r="P9" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V9" t="n">
-        <v>7</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH9" t="n">
-        <v>6.6</v>
+        <v>4.45</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>1.27</v>
       </c>
       <c r="P10" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="Q10" t="n">
         <v>4.3</v>
@@ -1760,7 +1760,7 @@
         <v>1.49</v>
       </c>
       <c r="V10" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="W10" t="n">
         <v>1.09</v>
@@ -1775,7 +1775,7 @@
         <v>1.19</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="AB10" t="n">
         <v>1.73</v>
@@ -1790,16 +1790,16 @@
         <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
-        <v>1.5</v>
+        <v>2.23</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>8.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.63</v>
+        <v>1.92</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="U11" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>8.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.45</v>
+        <v>3.72</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.33</v>
+        <v>7.1</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2012,34 +2012,34 @@
         <v>1.38</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.17</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AB12" t="n">
         <v>1.75</v>
@@ -2048,22 +2048,22 @@
         <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.92</v>
+        <v>2.23</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.79</v>
+        <v>2.09</v>
       </c>
       <c r="AH12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="M13" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.54</v>
       </c>
-      <c r="P13" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,34 +2258,34 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.97</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.34</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>2.23</v>
+        <v>1.51</v>
       </c>
       <c r="P14" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.92</v>
+        <v>3.28</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
         <v>7.1</v>
@@ -2297,37 +2297,37 @@
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.71</v>
       </c>
-      <c r="AD14" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH14" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
-        <v>4.15</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="P15" t="n">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.65</v>
+        <v>1.93</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3</v>
+        <v>2.64</v>
       </c>
       <c r="T15" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="U15" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.45</v>
+        <v>2.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.41</v>
+        <v>3.72</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="O16" t="n">
         <v>1.58</v>
@@ -2570,10 +2570,10 @@
         <v>3.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
         <v>2.62</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.65</v>
+        <v>3.24</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="T17" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB17" t="n">
         <v>2.25</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC17" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>1.99</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.05</v>
+        <v>6.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
-        <v>2.25</v>
+        <v>1.54</v>
       </c>
       <c r="P18" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.93</v>
+        <v>2.66</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="V18" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.88</v>
+        <v>4.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.72</v>
+        <v>2.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="AH18" t="n">
-        <v>7.1</v>
+        <v>4.55</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="M19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N19" t="n">
         <v>3.7</v>
       </c>
-      <c r="N19" t="n">
-        <v>6.1</v>
-      </c>
       <c r="O19" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.28</v>
+        <v>2.65</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="U19" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="V19" t="n">
-        <v>7.1</v>
+        <v>5.25</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.08</v>
+        <v>4.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="n">
-        <v>6.5</v>
+        <v>4.05</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.24</v>
+        <v>2.63</v>
       </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.08</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>6.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>4.25</v>
+        <v>3.85</v>
       </c>
       <c r="N21" t="n">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>1.48</v>
@@ -3230,10 +3230,10 @@
         <v>4.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
         <v>2.53</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.3</v>
       </c>
-      <c r="M22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N22" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P22" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AI22" t="n">
         <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.12</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="N24" t="n">
-        <v>1.55</v>
+        <v>9.5</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>1.26</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.53</v>
+        <v>4.75</v>
       </c>
       <c r="R24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.45</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AH24" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="M27" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.55</v>
+        <v>3.85</v>
       </c>
       <c r="O27" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P27" t="n">
-        <v>14.75</v>
+        <v>8.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T27" t="n">
-        <v>2.42</v>
+        <v>2.93</v>
       </c>
       <c r="U27" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>5.45</v>
+        <v>7.8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.85</v>
+        <v>3.02</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.7</v>
+        <v>3.62</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.03</v>
+        <v>1.73</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.8</v>
+        <v>7.3</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="M29" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="P29" t="n">
-        <v>8.6</v>
+        <v>14.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="T29" t="n">
-        <v>2.93</v>
+        <v>2.42</v>
       </c>
       <c r="U29" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="V29" t="n">
-        <v>7.8</v>
+        <v>5.45</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.02</v>
+        <v>3.85</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.62</v>
+        <v>2.7</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.73</v>
+        <v>2.03</v>
       </c>
       <c r="AH29" t="n">
-        <v>7.3</v>
+        <v>4.8</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="M31" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="O31" t="n">
         <v>1.44</v>
@@ -4538,10 +4538,10 @@
         <v>1.12</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z31" t="n">
         <v>1.18</v>
@@ -4550,10 +4550,10 @@
         <v>4.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD31" t="n">
         <v>2.6</v>
@@ -4670,10 +4670,10 @@
         <v>1.12</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z32" t="n">
         <v>1.18</v>
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="N34" t="n">
+        <v>6</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P34" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S34" t="n">
         <v>3.65</v>
       </c>
-      <c r="O34" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P34" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.35</v>
-      </c>
       <c r="T34" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="U34" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="V34" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z34" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y34" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA34" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.55</v>
+        <v>1.46</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AI34" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.05</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="O35" t="n">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="P35" t="n">
-        <v>19.75</v>
+        <v>6.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.24</v>
+        <v>2.6</v>
       </c>
       <c r="R35" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="S35" t="n">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="T35" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="V35" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>17</v>
+        <v>6.25</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="AA35" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.46</v>
+        <v>2.55</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AH35" t="n">
-        <v>3.84</v>
+        <v>9.25</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5192,22 +5192,22 @@
         <v>1.29</v>
       </c>
       <c r="V36" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="W36" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X36" t="n">
         <v>1.07</v>
       </c>
       <c r="Y36" t="n">
-        <v>7.5</v>
+        <v>7.17</v>
       </c>
       <c r="Z36" t="n">
         <v>1.42</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AB36" t="n">
         <v>2.25</v>
@@ -5216,13 +5216,13 @@
         <v>1.53</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AF36" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG36" t="n">
         <v>1.73</v>
@@ -5231,7 +5231,7 @@
         <v>10</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -657,20 +657,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -710,7 +710,7 @@
         <v>1.41</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
         <v>60</v>
@@ -747,12 +747,12 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38', '41', '57', '58', '90+2']</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '12', '60']</t>
         </is>
       </c>
       <c r="AL2" s="3" t="n">
@@ -780,106 +780,106 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.93</v>
+        <v>1.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.78</v>
+        <v>7.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.96</v>
+        <v>12.5</v>
       </c>
       <c r="O3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P3" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF3" t="n">
         <v>1.91</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '36', '67']</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -912,111 +912,111 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.2</v>
+        <v>1.93</v>
       </c>
       <c r="M4" t="n">
-        <v>7.1</v>
+        <v>3.78</v>
       </c>
       <c r="N4" t="n">
-        <v>12.5</v>
+        <v>2.96</v>
       </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="P4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O7" t="n">
         <v>1.8</v>
@@ -1352,7 +1352,7 @@
         <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
         <v>2.6</v>
@@ -1373,34 +1373,34 @@
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="AI7" t="n">
         <v>1.03</v>
@@ -1610,7 +1610,7 @@
         <v>1.27</v>
       </c>
       <c r="P9" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="Q9" t="n">
         <v>4.3</v>
@@ -1628,7 +1628,7 @@
         <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="W9" t="n">
         <v>1.09</v>
@@ -1643,7 +1643,7 @@
         <v>1.19</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="AB9" t="n">
         <v>1.73</v>
@@ -1658,16 +1658,16 @@
         <v>1.42</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>1.27</v>
       </c>
       <c r="P10" t="n">
-        <v>13.75</v>
+        <v>14</v>
       </c>
       <c r="Q10" t="n">
         <v>4.3</v>
@@ -1760,7 +1760,7 @@
         <v>1.49</v>
       </c>
       <c r="V10" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="W10" t="n">
         <v>1.09</v>
@@ -1775,7 +1775,7 @@
         <v>1.19</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="AB10" t="n">
         <v>1.73</v>
@@ -1790,16 +1790,16 @@
         <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="O11" t="n">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="P11" t="n">
-        <v>8.1</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.92</v>
+        <v>2.65</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>2.67</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.93</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V11" t="n">
-        <v>7.1</v>
+        <v>5.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.1</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.9</v>
+        <v>4.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.72</v>
+        <v>2.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.21</v>
+        <v>1.54</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>1.51</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>3.02</v>
+        <v>2.25</v>
       </c>
       <c r="P12" t="n">
-        <v>16.25</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.38</v>
+        <v>1.93</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>3.35</v>
+        <v>2.64</v>
       </c>
       <c r="T12" t="n">
-        <v>2.17</v>
+        <v>2.93</v>
       </c>
       <c r="U12" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC12" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD12" t="n">
-        <v>2.23</v>
+        <v>3.72</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>1.21</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="AH12" t="n">
-        <v>4</v>
+        <v>7.1</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.65</v>
+        <v>3.28</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="T13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB13" t="n">
         <v>2.25</v>
       </c>
-      <c r="U13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC13" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.15</v>
+        <v>1.71</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2267,13 +2267,13 @@
         <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P14" t="n">
         <v>8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="R14" t="n">
         <v>1.41</v>
@@ -2318,10 +2318,10 @@
         <v>1.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AH14" t="n">
         <v>6.5</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.25</v>
       </c>
-      <c r="P15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.93</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="V15" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="W15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.03</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y15" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG15" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH15" t="n">
-        <v>7.1</v>
+        <v>4.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2531,19 +2531,19 @@
         <v>3.65</v>
       </c>
       <c r="O16" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="P16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="R16" t="n">
         <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
         <v>2.38</v>
@@ -2552,7 +2552,7 @@
         <v>1.49</v>
       </c>
       <c r="V16" t="n">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="W16" t="n">
         <v>1.09</v>
@@ -2564,10 +2564,10 @@
         <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="AB16" t="n">
         <v>1.65</v>
@@ -2576,22 +2576,22 @@
         <v>2.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N17" t="n">
-        <v>4.5</v>
+        <v>1.56</v>
       </c>
       <c r="O17" t="n">
-        <v>1.52</v>
+        <v>3.02</v>
       </c>
       <c r="P17" t="n">
-        <v>8</v>
+        <v>16.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.24</v>
+        <v>1.38</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="T17" t="n">
-        <v>2.84</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.08</v>
+        <v>5.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>1.46</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.99</v>
+        <v>1.55</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AH17" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P18" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.54</v>
       </c>
-      <c r="P18" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AF18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH18" t="n">
         <v>4.05</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>4.55</v>
-      </c>
       <c r="AI18" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="P19" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="T19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.25</v>
       </c>
-      <c r="U19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA19" t="n">
+      <c r="AD19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH19" t="n">
         <v>4.65</v>
       </c>
-      <c r="AB19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>4.05</v>
-      </c>
       <c r="AI19" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
-        <v>1.5</v>
+        <v>2.23</v>
       </c>
       <c r="P20" t="n">
-        <v>12</v>
+        <v>8.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.63</v>
+        <v>1.92</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S20" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="T20" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="U20" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>8.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AA20" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.45</v>
+        <v>3.72</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.33</v>
+        <v>7.1</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>1.28</v>
       </c>
       <c r="M21" t="n">
-        <v>3.85</v>
+        <v>4.85</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O21" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="P21" t="n">
-        <v>16.75</v>
+        <v>9</v>
       </c>
       <c r="Q21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S21" t="n">
         <v>2.8</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.34</v>
-      </c>
       <c r="T21" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>5.45</v>
+        <v>6.3</v>
       </c>
       <c r="W21" t="n">
         <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>11</v>
+        <v>8.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.53</v>
+        <v>3.64</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.66</v>
+        <v>2.67</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.09</v>
+        <v>1.44</v>
       </c>
       <c r="AH21" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5.9</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N22" t="n">
-        <v>1.55</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>1.48</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>16.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.53</v>
+        <v>2.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="S22" t="n">
-        <v>2.6</v>
+        <v>3.34</v>
       </c>
       <c r="T22" t="n">
-        <v>3.2</v>
+        <v>2.32</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="V22" t="n">
-        <v>6.8</v>
+        <v>5.45</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.56</v>
+        <v>4.4</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC22" t="n">
         <v>2</v>
       </c>
-      <c r="AC22" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AD22" t="n">
-        <v>4.43</v>
+        <v>2.53</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>1.66</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.6</v>
+        <v>2.09</v>
       </c>
       <c r="AH22" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.65</v>
+        <v>5.4</v>
       </c>
       <c r="M23" t="n">
-        <v>2.8</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.99</v>
+        <v>2.45</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>4.8</v>
+        <v>2.66</v>
       </c>
       <c r="N24" t="n">
-        <v>9.5</v>
+        <v>2.87</v>
       </c>
       <c r="O24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC24" t="n">
         <v>1.36</v>
       </c>
-      <c r="V24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AD24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,76 +3842,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="M26" t="n">
         <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>15.25</v>
+        <v>9</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.81</v>
+        <v>3.46</v>
       </c>
       <c r="R26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z26" t="n">
         <v>1.28</v>
       </c>
-      <c r="S26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V26" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AA26" t="n">
-        <v>3.92</v>
+        <v>3.16</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.67</v>
+        <v>3.48</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.72</v>
+        <v>2.09</v>
       </c>
       <c r="AG26" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AH26" t="n">
-        <v>4.7</v>
+        <v>6.85</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,76 +3974,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
         <v>3.4</v>
       </c>
       <c r="N27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P27" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V27" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA27" t="n">
         <v>3.85</v>
       </c>
-      <c r="O27" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="P27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.02</v>
-      </c>
       <c r="AB27" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.62</v>
+        <v>2.7</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.73</v>
+        <v>2.03</v>
       </c>
       <c r="AH27" t="n">
-        <v>7.3</v>
+        <v>4.8</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
         <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="P28" t="n">
-        <v>9</v>
+        <v>15.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.46</v>
+        <v>2.81</v>
       </c>
       <c r="R28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.39</v>
       </c>
-      <c r="S28" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V28" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AF28" t="n">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="n">
-        <v>6.85</v>
+        <v>4.7</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="M29" t="n">
         <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O29" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P29" t="n">
-        <v>14.75</v>
+        <v>8.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T29" t="n">
-        <v>2.42</v>
+        <v>2.93</v>
       </c>
       <c r="U29" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>5.45</v>
+        <v>7.8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.85</v>
+        <v>3.02</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.7</v>
+        <v>3.62</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.03</v>
+        <v>1.73</v>
       </c>
       <c r="AH29" t="n">
-        <v>4.8</v>
+        <v>7.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4538,10 +4538,10 @@
         <v>1.12</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z31" t="n">
         <v>1.18</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M33" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P33" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S33" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U33" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
         <v>13</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH33" t="n">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="O34" t="n">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="P34" t="n">
-        <v>19.75</v>
+        <v>6.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.24</v>
+        <v>2.6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="S34" t="n">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="T34" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="U34" t="n">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="V34" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>17</v>
+        <v>6.25</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="AA34" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.46</v>
+        <v>2.55</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.84</v>
+        <v>9.25</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="N35" t="n">
+        <v>6</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P35" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S35" t="n">
         <v>3.65</v>
       </c>
-      <c r="O35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P35" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.35</v>
-      </c>
       <c r="T35" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="U35" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="V35" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z35" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y35" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA35" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.55</v>
+        <v>1.46</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AI35" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.05</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="M36" t="n">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="N36" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="O36" t="n">
         <v>1.73</v>
@@ -5180,10 +5180,10 @@
         <v>2.4</v>
       </c>
       <c r="R36" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="S36" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="T36" t="n">
         <v>3.25</v>
@@ -5192,46 +5192,46 @@
         <v>1.29</v>
       </c>
       <c r="V36" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="W36" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
         <v>1.07</v>
       </c>
       <c r="Y36" t="n">
-        <v>7.17</v>
+        <v>7</v>
       </c>
       <c r="Z36" t="n">
         <v>1.42</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AE36" t="n">
         <v>1.17</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG36" t="n">
         <v>1.73</v>
       </c>
       <c r="AH36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="M37" t="n">
-        <v>2.83</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="O37" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="P37" t="n">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="R37" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S37" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="U37" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="V37" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X37" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.25</v>
+        <v>3.9</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.48</v>
+        <v>1.62</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="AD37" t="n">
-        <v>4.75</v>
+        <v>2.75</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="n">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="M38" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P38" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T38" t="n">
         <v>3.75</v>
       </c>
-      <c r="N38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P38" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U38" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V38" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W38" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="Y38" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="AB38" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG38" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC38" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH38" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,22 +5558,22 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.03</v>
+        <v>2.56</v>
       </c>
       <c r="M39" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="N39" t="n">
-        <v>3.52</v>
+        <v>2.67</v>
       </c>
       <c r="O39" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="P39" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="R39" t="n">
         <v>1.53</v>
@@ -5582,10 +5582,10 @@
         <v>2.38</v>
       </c>
       <c r="T39" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U39" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V39" t="n">
         <v>11</v>
@@ -5594,40 +5594,40 @@
         <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AD39" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH39" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -1317,20 +1317,20 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '36']</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
-        <v>3.38</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>3.64</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.64</v>
       </c>
-      <c r="P8" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V8" t="n">
-        <v>7</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH8" t="n">
-        <v>6.6</v>
+        <v>4.45</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="M10" t="n">
-        <v>4.6</v>
+        <v>3.38</v>
       </c>
       <c r="N10" t="n">
-        <v>8.300000000000001</v>
+        <v>3.64</v>
       </c>
       <c r="O10" t="n">
-        <v>1.27</v>
+        <v>1.64</v>
       </c>
       <c r="P10" t="n">
-        <v>14</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.3</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="T10" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.98</v>
+        <v>3.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.45</v>
+        <v>6.6</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.65</v>
+        <v>3.24</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB11" t="n">
         <v>2.25</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC11" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>1.99</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2003,19 +2003,19 @@
         <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="P12" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="T12" t="n">
         <v>2.93</v>
@@ -2024,22 +2024,22 @@
         <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AB12" t="n">
         <v>2.1</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>1.56</v>
       </c>
       <c r="O13" t="n">
-        <v>1.51</v>
+        <v>3.02</v>
       </c>
       <c r="P13" t="n">
-        <v>8</v>
+        <v>16.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.28</v>
+        <v>1.38</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="T13" t="n">
-        <v>2.84</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.08</v>
+        <v>5.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>1.46</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.02</v>
+        <v>1.55</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.71</v>
+        <v>2.04</v>
       </c>
       <c r="AH13" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.24</v>
+        <v>2.63</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="V14" t="n">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.08</v>
+        <v>5</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>6.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="P15" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="T15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC15" t="n">
         <v>2.25</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AD15" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.33</v>
+        <v>4.65</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P16" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.54</v>
       </c>
-      <c r="P16" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>1.56</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.02</v>
+        <v>1.51</v>
       </c>
       <c r="P17" t="n">
-        <v>16.25</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.38</v>
+        <v>3.28</v>
       </c>
       <c r="R17" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>2.84</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.1</v>
+        <v>3.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.46</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2.02</v>
       </c>
-      <c r="AD17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AG17" t="n">
-        <v>2.04</v>
+        <v>1.71</v>
       </c>
       <c r="AH17" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.65</v>
+        <v>1.93</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>2.64</v>
       </c>
       <c r="T18" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="U18" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>17</v>
+        <v>7.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.65</v>
+        <v>2.88</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.3</v>
+        <v>3.72</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.05</v>
+        <v>7.1</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2927,19 +2927,19 @@
         <v>3.65</v>
       </c>
       <c r="O19" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="P19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="R19" t="n">
         <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
         <v>2.38</v>
@@ -2948,7 +2948,7 @@
         <v>1.49</v>
       </c>
       <c r="V19" t="n">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="W19" t="n">
         <v>1.09</v>
@@ -2960,10 +2960,10 @@
         <v>10</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="AB19" t="n">
         <v>1.65</v>
@@ -2972,22 +2972,22 @@
         <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="P20" t="n">
-        <v>8.1</v>
+        <v>12</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.92</v>
+        <v>2.65</v>
       </c>
       <c r="R20" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>2.67</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.93</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V20" t="n">
-        <v>7.1</v>
+        <v>5.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.1</v>
+        <v>17</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.9</v>
+        <v>4.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.72</v>
+        <v>2.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.21</v>
+        <v>1.54</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>7.1</v>
+        <v>4.05</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.28</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>4.85</v>
+        <v>2.66</v>
       </c>
       <c r="N21" t="n">
-        <v>12</v>
+        <v>2.87</v>
       </c>
       <c r="O21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.36</v>
       </c>
-      <c r="V21" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD21" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,76 +3446,76 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V23" t="n">
         <v>5.4</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="W23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD23" t="n">
         <v>2.5</v>
       </c>
-      <c r="T23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V23" t="n">
-        <v>7</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>4.68</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.28</v>
+        <v>1.65</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.55</v>
+        <v>2.11</v>
       </c>
       <c r="AH23" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,76 +3578,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="M24" t="n">
-        <v>2.66</v>
+        <v>3.13</v>
       </c>
       <c r="N24" t="n">
-        <v>2.87</v>
+        <v>1.67</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>1.28</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>4.85</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O25" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="P25" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Q25" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S25" t="n">
         <v>2.8</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.25</v>
       </c>
-      <c r="S25" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V25" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE25" t="n">
+      <c r="AF25" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.44</v>
       </c>
-      <c r="AF25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AH25" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3851,43 +3851,43 @@
         <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="P26" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.46</v>
+        <v>3.02</v>
       </c>
       <c r="R26" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="U26" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="AB26" t="n">
         <v>1.89</v>
@@ -3896,22 +3896,22 @@
         <v>1.81</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.48</v>
+        <v>3.62</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AH26" t="n">
-        <v>6.85</v>
+        <v>7.3</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -4247,43 +4247,43 @@
         <v>3.85</v>
       </c>
       <c r="O29" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="P29" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.02</v>
+        <v>3.46</v>
       </c>
       <c r="R29" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="T29" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="U29" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V29" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.02</v>
+        <v>3.16</v>
       </c>
       <c r="AB29" t="n">
         <v>1.89</v>
@@ -4292,22 +4292,22 @@
         <v>1.81</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.62</v>
+        <v>3.48</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AH29" t="n">
-        <v>7.3</v>
+        <v>6.85</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M30" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P30" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S30" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T30" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U30" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V30" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
         <v>13</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4802,10 +4802,10 @@
         <v>1.12</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z33" t="n">
         <v>1.18</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="M37" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P37" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T37" t="n">
         <v>3.75</v>
       </c>
-      <c r="N37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P37" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U37" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V37" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W37" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="Y37" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="AB37" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG37" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC37" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH37" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="M38" t="n">
-        <v>2.91</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>3.52</v>
+        <v>2.7</v>
       </c>
       <c r="O38" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="P38" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="R38" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="U38" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="V38" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W38" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X38" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.43</v>
+        <v>1.62</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.49</v>
+        <v>2.18</v>
       </c>
       <c r="AD38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH38" t="n">
         <v>5.5</v>
       </c>
-      <c r="AE38" t="n">
+      <c r="AI38" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1.04</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,34 +1862,34 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
-        <v>1.52</v>
+        <v>2.23</v>
       </c>
       <c r="P11" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.24</v>
+        <v>1.92</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="T11" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="U11" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
         <v>7.1</v>
@@ -1901,37 +1901,37 @@
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,34 +1994,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.23</v>
+        <v>1.52</v>
       </c>
       <c r="P12" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.92</v>
+        <v>3.24</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
         <v>7.1</v>
@@ -2033,37 +2033,37 @@
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AH12" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N13" t="n">
-        <v>1.56</v>
+        <v>3.65</v>
       </c>
       <c r="O13" t="n">
-        <v>3.02</v>
+        <v>1.54</v>
       </c>
       <c r="P13" t="n">
-        <v>16.25</v>
+        <v>15</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.38</v>
+        <v>2.66</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="U13" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="V13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AI13" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.18</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="M14" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.63</v>
+        <v>1.93</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5</v>
+        <v>2.64</v>
       </c>
       <c r="T14" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="U14" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AA14" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.45</v>
+        <v>3.72</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.33</v>
+        <v>7.1</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2486,121 +2486,121 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.98</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N16" t="n">
-        <v>3.7</v>
+        <v>1.56</v>
       </c>
       <c r="O16" t="n">
-        <v>1.53</v>
+        <v>3.02</v>
       </c>
       <c r="P16" t="n">
-        <v>12</v>
+        <v>16.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.65</v>
+        <v>1.38</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T16" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U16" t="n">
         <v>1.55</v>
       </c>
       <c r="V16" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.45</v>
+        <v>5.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29', '39']</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47', '50']</t>
         </is>
       </c>
       <c r="AL16" s="3" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="M17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S17" t="n">
         <v>3.3</v>
       </c>
-      <c r="N17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P17" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.6</v>
-      </c>
       <c r="T17" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>7.1</v>
+        <v>5.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.08</v>
+        <v>4.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>6.5</v>
+        <v>4.05</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.25</v>
+        <v>1.51</v>
       </c>
       <c r="P18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.93</v>
+        <v>3.28</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AH18" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="N19" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="P19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="U19" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="V19" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z19" t="n">
         <v>1.18</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3089,13 +3089,13 @@
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.65</v>
+        <v>4.45</v>
       </c>
       <c r="AB20" t="n">
         <v>1.7</v>
@@ -3116,10 +3116,10 @@
         <v>2.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="N21" t="n">
-        <v>2.87</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>16.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,16 +3288,16 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -3310,84 +3310,84 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>1.28</v>
       </c>
       <c r="M22" t="n">
-        <v>3.85</v>
+        <v>4.85</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O22" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="P22" t="n">
-        <v>16.75</v>
+        <v>9</v>
       </c>
       <c r="Q22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
         <v>2.8</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.34</v>
-      </c>
       <c r="T22" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="U22" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
-        <v>5.45</v>
+        <v>6.3</v>
       </c>
       <c r="W22" t="n">
         <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>11</v>
+        <v>8.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC22" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.53</v>
+        <v>3.64</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.66</v>
+        <v>2.67</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.09</v>
+        <v>1.44</v>
       </c>
       <c r="AH22" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53', '90+1']</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,16 +3420,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -3442,84 +3442,84 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.85</v>
+        <v>2.66</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>2.87</v>
       </c>
       <c r="O23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AC23" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -3561,20 +3561,20 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45', '90+2']</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AL24" s="3" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,76 +3710,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.28</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>4.85</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="P25" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.75</v>
+        <v>2.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8</v>
+        <v>3.42</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="U25" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="V25" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>8.1</v>
+        <v>11</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.4</v>
+        <v>4.45</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.64</v>
+        <v>2.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.44</v>
+        <v>2.11</v>
       </c>
       <c r="AH25" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="M28" t="n">
         <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O28" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="P28" t="n">
-        <v>15.25</v>
+        <v>9</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.81</v>
+        <v>3.46</v>
       </c>
       <c r="R28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V28" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z28" t="n">
         <v>1.28</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V28" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AA28" t="n">
-        <v>3.92</v>
+        <v>3.16</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.67</v>
+        <v>3.48</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.72</v>
+        <v>2.09</v>
       </c>
       <c r="AG28" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.7</v>
+        <v>6.85</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="M29" t="n">
         <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="P29" t="n">
-        <v>9</v>
+        <v>15.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.46</v>
+        <v>2.81</v>
       </c>
       <c r="R29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V29" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.39</v>
       </c>
-      <c r="S29" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V29" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AF29" t="n">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="n">
-        <v>6.85</v>
+        <v>4.7</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4406,10 +4406,10 @@
         <v>1.12</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z30" t="n">
         <v>1.18</v>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O33" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P33" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R33" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S33" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T33" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="U33" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V33" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="W33" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X33" t="n">
         <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="n">
-        <v>4.65</v>
+        <v>4.3</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,76 +4898,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="N34" t="n">
+        <v>6</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P34" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S34" t="n">
         <v>3.65</v>
       </c>
-      <c r="O34" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P34" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.35</v>
-      </c>
       <c r="T34" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="U34" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="V34" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z34" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y34" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA34" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.55</v>
+        <v>1.46</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AI34" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.05</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,76 +5030,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="O35" t="n">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="P35" t="n">
-        <v>19.75</v>
+        <v>6.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.24</v>
+        <v>2.6</v>
       </c>
       <c r="R35" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="S35" t="n">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="T35" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="V35" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>17</v>
+        <v>6.25</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="AA35" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.46</v>
+        <v>2.55</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AH35" t="n">
-        <v>3.84</v>
+        <v>9.25</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,22 +5294,22 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.03</v>
+        <v>2.56</v>
       </c>
       <c r="M37" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="N37" t="n">
-        <v>3.52</v>
+        <v>2.67</v>
       </c>
       <c r="O37" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="P37" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="R37" t="n">
         <v>1.53</v>
@@ -5318,10 +5318,10 @@
         <v>2.38</v>
       </c>
       <c r="T37" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U37" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V37" t="n">
         <v>11</v>
@@ -5330,40 +5330,40 @@
         <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AD37" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH37" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,76 +5426,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="M38" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P38" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T38" t="n">
         <v>3.75</v>
       </c>
-      <c r="N38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P38" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U38" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V38" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W38" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="Y38" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="AB38" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG38" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC38" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH38" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="M39" t="n">
-        <v>2.83</v>
+        <v>3.75</v>
       </c>
       <c r="N39" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="O39" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="P39" t="n">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="R39" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S39" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="U39" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="V39" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X39" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y39" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.25</v>
+        <v>3.9</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.48</v>
+        <v>1.62</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.75</v>
+        <v>2.75</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AH39" t="n">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6</v>
+        <v>3.38</v>
       </c>
       <c r="N9" t="n">
-        <v>8.300000000000001</v>
+        <v>3.64</v>
       </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>1.64</v>
       </c>
       <c r="P9" t="n">
-        <v>13.75</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.3</v>
+        <v>2.63</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="T9" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.38</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>3.64</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="P10" t="n">
-        <v>8.699999999999999</v>
+        <v>13.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.63</v>
+        <v>4.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>2.77</v>
+        <v>3.08</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.1</v>
+        <v>3.94</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.35</v>
+        <v>2.56</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,34 +1862,34 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.23</v>
+        <v>1.52</v>
       </c>
       <c r="P11" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.92</v>
+        <v>3.24</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
         <v>7.1</v>
@@ -1901,37 +1901,37 @@
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AH11" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2003,13 +2003,13 @@
         <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P12" t="n">
         <v>8</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="R12" t="n">
         <v>1.41</v>
@@ -2054,10 +2054,10 @@
         <v>1.25</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AH12" t="n">
         <v>6.5</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
-        <v>1.54</v>
+        <v>2.23</v>
       </c>
       <c r="P13" t="n">
-        <v>15</v>
+        <v>8.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.66</v>
+        <v>1.92</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="T13" t="n">
-        <v>2.38</v>
+        <v>2.93</v>
       </c>
       <c r="U13" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.05</v>
+        <v>2.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.6</v>
+        <v>3.72</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.55</v>
+        <v>7.1</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,121 +2222,121 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.5</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.25</v>
       </c>
-      <c r="P14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.93</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="V14" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="W14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.03</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y14" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG14" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH14" t="n">
-        <v>7.1</v>
+        <v>4.33</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['49', '63']</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AL14" s="3" t="n">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="P15" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="V15" t="n">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.95</v>
+        <v>4.45</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,121 +2486,121 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>1.56</v>
+        <v>3.65</v>
       </c>
       <c r="O16" t="n">
-        <v>3.02</v>
+        <v>1.58</v>
       </c>
       <c r="P16" t="n">
-        <v>16.25</v>
+        <v>14.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.38</v>
+        <v>2.56</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="U16" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>4</v>
+        <v>4.65</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>['29', '39']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>['47', '50']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL16" s="3" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.65</v>
+        <v>1.93</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>2.64</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>17</v>
+        <v>7.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.65</v>
+        <v>2.88</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.3</v>
+        <v>3.72</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.05</v>
+        <v>7.1</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="M18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P18" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.3</v>
       </c>
-      <c r="N18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P18" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.6</v>
-      </c>
       <c r="T18" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="V18" t="n">
-        <v>7.1</v>
+        <v>5.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.08</v>
+        <v>4.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>6.5</v>
+        <v>4.05</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="P19" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="V19" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z19" t="n">
         <v>1.18</v>
       </c>
       <c r="AA19" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,121 +3014,121 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.98</v>
+        <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N20" t="n">
-        <v>3.7</v>
+        <v>1.56</v>
       </c>
       <c r="O20" t="n">
-        <v>1.53</v>
+        <v>3.02</v>
       </c>
       <c r="P20" t="n">
-        <v>12</v>
+        <v>16.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.65</v>
+        <v>1.38</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T20" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U20" t="n">
         <v>1.55</v>
       </c>
       <c r="V20" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.45</v>
+        <v>5.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29', '39']</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47', '50']</t>
         </is>
       </c>
       <c r="AL20" s="3" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,16 +3156,16 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -3178,84 +3178,84 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.85</v>
+        <v>2.66</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>2.87</v>
       </c>
       <c r="O21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>16.75</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,16 +3420,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -3442,84 +3442,84 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="N23" t="n">
-        <v>2.87</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.4</v>
+        <v>4.45</v>
       </c>
       <c r="AB23" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,111 +3552,111 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P24" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC24" t="n">
         <v>2</v>
       </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AD24" t="n">
-        <v>4.68</v>
+        <v>2.53</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.55</v>
+        <v>2.09</v>
       </c>
       <c r="AH24" t="n">
-        <v>9</v>
+        <v>4.6</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>['45', '90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL24" s="3" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,111 +3684,111 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>5.4</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>3.13</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>1.67</v>
       </c>
       <c r="O25" t="n">
-        <v>1.48</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.8</v>
+        <v>1.53</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>3.42</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="V25" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI25" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y25" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45', '90+2']</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AL25" s="3" t="n">
@@ -3851,43 +3851,43 @@
         <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.02</v>
+        <v>3.46</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="T26" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V26" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.02</v>
+        <v>3.16</v>
       </c>
       <c r="AB26" t="n">
         <v>1.89</v>
@@ -3896,22 +3896,22 @@
         <v>1.81</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.62</v>
+        <v>3.48</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AH26" t="n">
-        <v>7.3</v>
+        <v>6.85</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3983,13 +3983,13 @@
         <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="P27" t="n">
-        <v>14.75</v>
+        <v>15.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="R27" t="n">
         <v>1.28</v>
@@ -3998,16 +3998,16 @@
         <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V27" t="n">
-        <v>5.45</v>
+        <v>5.35</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
@@ -4016,10 +4016,10 @@
         <v>9.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="AB27" t="n">
         <v>2.2</v>
@@ -4028,22 +4028,22 @@
         <v>1.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,76 +4106,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
         <v>3.4</v>
       </c>
       <c r="N28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P28" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA28" t="n">
         <v>3.85</v>
       </c>
-      <c r="O28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P28" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V28" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.16</v>
-      </c>
       <c r="AB28" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.48</v>
+        <v>2.7</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.09</v>
+        <v>1.7</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="AH28" t="n">
-        <v>6.85</v>
+        <v>4.8</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,76 +4238,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="M29" t="n">
         <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O29" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="P29" t="n">
-        <v>15.25</v>
+        <v>8.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T29" t="n">
-        <v>2.4</v>
+        <v>2.93</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>5.35</v>
+        <v>7.8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.92</v>
+        <v>3.02</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.67</v>
+        <v>3.62</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="AG29" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AH29" t="n">
-        <v>4.7</v>
+        <v>7.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,76 +4370,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,76 +4502,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O31" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P31" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R31" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="U31" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V31" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="W31" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
         <v>13</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AH31" t="n">
-        <v>4.65</v>
+        <v>4.3</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,76 +4634,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,76 +4766,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M33" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P33" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S33" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U33" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X33" t="n">
         <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH33" t="n">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="M36" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N36" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O36" t="n">
         <v>1.73</v>
@@ -5180,7 +5180,7 @@
         <v>2.4</v>
       </c>
       <c r="R36" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="S36" t="n">
         <v>2.4</v>
@@ -5192,7 +5192,7 @@
         <v>1.29</v>
       </c>
       <c r="V36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W36" t="n">
         <v>1.01</v>
@@ -5201,34 +5201,34 @@
         <v>1.07</v>
       </c>
       <c r="Y36" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Z36" t="n">
         <v>1.42</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB36" t="n">
         <v>2.48</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AE36" t="n">
         <v>1.17</v>
       </c>
       <c r="AF36" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG36" t="n">
         <v>1.73</v>
       </c>
       <c r="AH36" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI36" t="n">
         <v>1.05</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,76 +5294,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="M37" t="n">
-        <v>2.83</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="O37" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="P37" t="n">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="R37" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S37" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="U37" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="V37" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X37" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.25</v>
+        <v>3.9</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.48</v>
+        <v>1.62</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="AD37" t="n">
-        <v>4.75</v>
+        <v>2.75</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="n">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,22 +5426,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.03</v>
+        <v>2.56</v>
       </c>
       <c r="M38" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="N38" t="n">
-        <v>3.52</v>
+        <v>2.67</v>
       </c>
       <c r="O38" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="P38" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="R38" t="n">
         <v>1.53</v>
@@ -5450,10 +5450,10 @@
         <v>2.38</v>
       </c>
       <c r="T38" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U38" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V38" t="n">
         <v>11</v>
@@ -5462,40 +5462,40 @@
         <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AD38" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH38" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,76 +5558,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="M39" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P39" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T39" t="n">
         <v>3.75</v>
       </c>
-      <c r="N39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P39" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U39" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W39" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="Y39" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="AB39" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG39" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC39" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH39" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>

--- a/jogos_2025-08-12.xlsx
+++ b/jogos_2025-08-12.xlsx
@@ -1665,119 +1665,119 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N10" t="n">
-        <v>3.65</v>
+        <v>1.56</v>
       </c>
       <c r="O10" t="n">
-        <v>2.23</v>
+        <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.55</v>
+        <v>1.65</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T10" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="V10" t="n">
         <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>4.05</v>
+        <v>5.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29', '39']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47', '50']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.13</v>
+        <v>1.1</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.54</v>
+        <v>3.02</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.66</v>
+        <v>1.38</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45881.58333333334</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45881.58333333334</v>
@@ -1933,109 +1933,109 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.17</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.4</v>
+        <v>2.93</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="T12" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
         <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="X12" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="Y12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI12" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['31', '43', '51', '67', '69']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>3.28</v>
+        <v>1.93</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45881.58333333334</v>
@@ -2052,119 +2052,119 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>1.98</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>1.56</v>
+        <v>3.7</v>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>2.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.65</v>
+        <v>4.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
         <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>5.1</v>
+        <v>4.65</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['29', '39']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['47', '50']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.02</v>
+        <v>1.53</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.38</v>
+        <v>2.65</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45881.58333333334</v>
@@ -2181,119 +2181,119 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="M14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S14" t="n">
         <v>3.6</v>
       </c>
-      <c r="N14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T14" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="U14" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X14" t="n">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z14" t="n">
         <v>2.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['49', '63']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45881.58333333334</v>
@@ -2320,109 +2320,109 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>2.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.91</v>
+        <v>4.55</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="V15" t="n">
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
-        <v>2.9</v>
+        <v>4.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.72</v>
+        <v>2.6</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>1.21</v>
       </c>
-      <c r="AC15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['2', '55']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>2.13</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.23</v>
+        <v>1.54</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.92</v>
+        <v>2.66</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45881.58333333334</v>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>3.13</v>
+        <v>2.66</v>
       </c>
       <c r="N16" t="n">
-        <v>1.67</v>
+        <v>2.87</v>
       </c>
       <c r="O16" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.5</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.42</v>
-      </c>
       <c r="X16" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['45', '90+2']</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45881.60416666666</v>
@@ -2587,20 +2587,20 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2622,10 +2622,10 @@
         <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="T17" t="n">
         <v>2.32</v>
@@ -2637,10 +2637,10 @@
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="Y17" t="n">
         <v>1.8</v>
@@ -2649,25 +2649,25 @@
         <v>2</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61', '83', '90+4']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '42']</t>
         </is>
       </c>
       <c r="AG17" t="n">
@@ -2707,16 +2707,16 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2733,65 +2733,65 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>1.28</v>
       </c>
       <c r="M18" t="n">
-        <v>2.66</v>
+        <v>4.85</v>
       </c>
       <c r="N18" t="n">
-        <v>2.87</v>
+        <v>12</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="X18" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>['53', '90+1']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45881.60416666666</v>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.28</v>
+        <v>5.4</v>
       </c>
       <c r="M19" t="n">
-        <v>4.85</v>
+        <v>3.13</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>1.67</v>
       </c>
       <c r="O19" t="n">
-        <v>1.82</v>
+        <v>5.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.8</v>
+        <v>2.38</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="V19" t="n">
         <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="X19" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.07</v>
+        <v>2.45</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.64</v>
+        <v>4.68</v>
       </c>
       <c r="AB19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['45', '90+2']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC19" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['53', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
+      <c r="AH19" t="n">
         <v>1.14</v>
       </c>
-      <c r="AH19" t="n">
-        <v>3.02</v>
-      </c>
       <c r="AI19" t="n">
-        <v>1.26</v>
+        <v>3.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>4.75</v>
+        <v>1.53</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45881.60416666666</v>
@@ -2965,109 +2965,109 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="M20" t="n">
         <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O20" t="n">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="P20" t="n">
-        <v>2.41</v>
+        <v>2.09</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.4</v>
+        <v>2.93</v>
       </c>
       <c r="U20" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="X20" t="n">
-        <v>3.92</v>
+        <v>3.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.67</v>
+        <v>3.62</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="AD20" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
+          <t>['38', '79', '86']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45881.63541666666</v>
@@ -3094,16 +3094,16 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -3120,65 +3120,65 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="M21" t="n">
         <v>3.4</v>
       </c>
       <c r="N21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X21" t="n">
         <v>3.85</v>
       </c>
-      <c r="O21" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.02</v>
-      </c>
       <c r="Y21" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.62</v>
+        <v>2.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.73</v>
+        <v>2.03</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['38', '79', '86']</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45881.63541666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X27" t="n">
         <v>2.25</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.9</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.62</v>
+        <v>2.48</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.18</v>
+        <v>1.47</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.75</v>
+        <v>4.75</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
         <v>1.42</v>
       </c>
-      <c r="AC27" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['38', '50', '88']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45881.89583333334</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,109 +4126,109 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="M29" t="n">
-        <v>2.83</v>
+        <v>3.75</v>
       </c>
       <c r="N29" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="O29" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['38', '50', '88']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AJ29" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45881.89583333334</v>
